--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA809"/>
+  <dimension ref="A1:AA814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -80292,6 +80292,519 @@
       <c r="Z809" s="2" t="inlineStr"/>
       <c r="AA809" s="2" t="inlineStr"/>
     </row>
+    <row r="810">
+      <c r="A810" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B810" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C810" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D810" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E810" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F810" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G810" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I810" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J810" s="2" t="inlineStr"/>
+      <c r="K810" s="2" t="inlineStr"/>
+      <c r="L810" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M810" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N810" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O810" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P810" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q810" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R810" s="2" t="inlineStr"/>
+      <c r="S810" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T810" s="2" t="inlineStr"/>
+      <c r="U810" s="2" t="inlineStr"/>
+      <c r="V810" s="2" t="inlineStr"/>
+      <c r="W810" s="2" t="inlineStr">
+        <is>
+          <t>Gerhard Kracher</t>
+        </is>
+      </c>
+      <c r="X810" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y810" s="2" t="inlineStr"/>
+      <c r="Z810" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA810" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gerhard-kracher-5568b1149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D811" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G811" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I811" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J811" s="2" t="inlineStr"/>
+      <c r="K811" s="2" t="inlineStr"/>
+      <c r="L811" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M811" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N811" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O811" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P811" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q811" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R811" s="2" t="inlineStr"/>
+      <c r="S811" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T811" s="2" t="inlineStr"/>
+      <c r="U811" s="2" t="inlineStr"/>
+      <c r="V811" s="2" t="inlineStr"/>
+      <c r="W811" s="2" t="inlineStr">
+        <is>
+          <t>Hans Martin</t>
+        </is>
+      </c>
+      <c r="X811" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Manager/ Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y811" s="2" t="inlineStr"/>
+      <c r="Z811" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA811" s="2" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B812" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C812" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D812" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E812" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F812" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G812" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I812" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J812" s="2" t="inlineStr"/>
+      <c r="K812" s="2" t="inlineStr"/>
+      <c r="L812" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M812" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N812" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O812" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P812" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q812" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R812" s="2" t="inlineStr"/>
+      <c r="S812" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T812" s="2" t="inlineStr"/>
+      <c r="U812" s="2" t="inlineStr"/>
+      <c r="V812" s="2" t="inlineStr"/>
+      <c r="W812" s="2" t="inlineStr">
+        <is>
+          <t>Yvonne Kracher</t>
+        </is>
+      </c>
+      <c r="X812" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Sales</t>
+        </is>
+      </c>
+      <c r="Y812" s="2" t="inlineStr"/>
+      <c r="Z812" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA812" s="2" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D813" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I813" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J813" s="2" t="inlineStr"/>
+      <c r="K813" s="2" t="inlineStr"/>
+      <c r="L813" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M813" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N813" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O813" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P813" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q813" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R813" s="2" t="inlineStr"/>
+      <c r="S813" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T813" s="2" t="inlineStr"/>
+      <c r="U813" s="2" t="inlineStr"/>
+      <c r="V813" s="2" t="inlineStr"/>
+      <c r="W813" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Wolf</t>
+        </is>
+      </c>
+      <c r="X813" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y813" s="2" t="inlineStr"/>
+      <c r="Z813" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA813" s="2" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="B814" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="C814" s="2" t="inlineStr">
+        <is>
+          <t>54996</t>
+        </is>
+      </c>
+      <c r="D814" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E814" s="2" t="inlineStr">
+        <is>
+          <t>Eisenberg an der Pinka</t>
+        </is>
+      </c>
+      <c r="F814" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Oberwart</t>
+        </is>
+      </c>
+      <c r="G814" s="2" t="inlineStr">
+        <is>
+          <t>1 Am Naturpark</t>
+        </is>
+      </c>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="I814" s="2" t="inlineStr">
+        <is>
+          <t>https://vinothek.eisenberg.at</t>
+        </is>
+      </c>
+      <c r="J814" s="2" t="inlineStr"/>
+      <c r="K814" s="2" t="inlineStr"/>
+      <c r="L814" s="2" t="inlineStr"/>
+      <c r="M814" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N814" s="2" t="inlineStr">
+        <is>
+          <t>wein@eisenberg.at</t>
+        </is>
+      </c>
+      <c r="O814" s="2" t="inlineStr">
+        <is>
+          <t>+43 3365 2666</t>
+        </is>
+      </c>
+      <c r="P814" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q814" s="2" t="inlineStr"/>
+      <c r="R814" s="2" t="inlineStr"/>
+      <c r="S814" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinothekeisenberg/</t>
+        </is>
+      </c>
+      <c r="T814" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinothek_eisenberg/</t>
+        </is>
+      </c>
+      <c r="U814" s="2" t="inlineStr"/>
+      <c r="V814" s="2" t="inlineStr"/>
+      <c r="W814" s="2" t="inlineStr"/>
+      <c r="X814" s="2" t="inlineStr"/>
+      <c r="Y814" s="2" t="inlineStr"/>
+      <c r="Z814" s="2" t="inlineStr"/>
+      <c r="AA814" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA814"/>
+  <dimension ref="A1:AA820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -80805,6 +80805,632 @@
       <c r="Z814" s="2" t="inlineStr"/>
       <c r="AA814" s="2" t="inlineStr"/>
     </row>
+    <row r="815">
+      <c r="A815" s="2" t="inlineStr">
+        <is>
+          <t>Neun Weine Gmbh</t>
+        </is>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>Neun Weine Gmbh</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="inlineStr">
+        <is>
+          <t>61544</t>
+        </is>
+      </c>
+      <c r="D815" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="inlineStr">
+        <is>
+          <t>Neutal</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Oberpullendorf</t>
+        </is>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>7 Werner von Siemens-Straße</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="I815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neunweine.at, https://www.neunweine.de</t>
+        </is>
+      </c>
+      <c r="J815" s="2" t="inlineStr"/>
+      <c r="K815" s="2" t="inlineStr"/>
+      <c r="L815" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M815" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N815" s="2" t="inlineStr">
+        <is>
+          <t>michael@neunweine.at</t>
+        </is>
+      </c>
+      <c r="O815" s="2" t="inlineStr">
+        <is>
+          <t>+43 720 3030505099</t>
+        </is>
+      </c>
+      <c r="P815" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q815" s="2" t="inlineStr">
+        <is>
+          <t>FN432466f</t>
+        </is>
+      </c>
+      <c r="R815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neun-weine/</t>
+        </is>
+      </c>
+      <c r="S815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/neunweine/</t>
+        </is>
+      </c>
+      <c r="T815" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neunweine/</t>
+        </is>
+      </c>
+      <c r="U815" s="2" t="inlineStr"/>
+      <c r="V815" s="2" t="inlineStr"/>
+      <c r="W815" s="2" t="inlineStr">
+        <is>
+          <t>Michael Pruenner</t>
+        </is>
+      </c>
+      <c r="X815" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y815" s="2" t="inlineStr"/>
+      <c r="Z815" s="2" t="inlineStr"/>
+      <c r="AA815" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/michael-pruenner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C816" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D816" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E816" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F816" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G816" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I816" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J816" s="2" t="inlineStr"/>
+      <c r="K816" s="2" t="inlineStr"/>
+      <c r="L816" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M816" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N816" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O816" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P816" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q816" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R816" s="2" t="inlineStr"/>
+      <c r="S816" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T816" s="2" t="inlineStr"/>
+      <c r="U816" s="2" t="inlineStr"/>
+      <c r="V816" s="2" t="inlineStr"/>
+      <c r="W816" s="2" t="inlineStr">
+        <is>
+          <t>Gerhard Kracher</t>
+        </is>
+      </c>
+      <c r="X816" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y816" s="2" t="inlineStr"/>
+      <c r="Z816" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA816" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gerhard-kracher-5568b1149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D817" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I817" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J817" s="2" t="inlineStr"/>
+      <c r="K817" s="2" t="inlineStr"/>
+      <c r="L817" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M817" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N817" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O817" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P817" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q817" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R817" s="2" t="inlineStr"/>
+      <c r="S817" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T817" s="2" t="inlineStr"/>
+      <c r="U817" s="2" t="inlineStr"/>
+      <c r="V817" s="2" t="inlineStr"/>
+      <c r="W817" s="2" t="inlineStr">
+        <is>
+          <t>Hans Martin</t>
+        </is>
+      </c>
+      <c r="X817" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Manager/ Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y817" s="2" t="inlineStr"/>
+      <c r="Z817" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA817" s="2" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B818" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C818" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D818" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E818" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F818" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G818" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I818" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J818" s="2" t="inlineStr"/>
+      <c r="K818" s="2" t="inlineStr"/>
+      <c r="L818" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M818" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N818" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O818" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P818" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q818" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R818" s="2" t="inlineStr"/>
+      <c r="S818" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T818" s="2" t="inlineStr"/>
+      <c r="U818" s="2" t="inlineStr"/>
+      <c r="V818" s="2" t="inlineStr"/>
+      <c r="W818" s="2" t="inlineStr">
+        <is>
+          <t>Yvonne Kracher</t>
+        </is>
+      </c>
+      <c r="X818" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Sales</t>
+        </is>
+      </c>
+      <c r="Y818" s="2" t="inlineStr"/>
+      <c r="Z818" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA818" s="2" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D819" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Neusiedl am See</t>
+        </is>
+      </c>
+      <c r="G819" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I819" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J819" s="2" t="inlineStr"/>
+      <c r="K819" s="2" t="inlineStr"/>
+      <c r="L819" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M819" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N819" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O819" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P819" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q819" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R819" s="2" t="inlineStr"/>
+      <c r="S819" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T819" s="2" t="inlineStr"/>
+      <c r="U819" s="2" t="inlineStr"/>
+      <c r="V819" s="2" t="inlineStr"/>
+      <c r="W819" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Wolf</t>
+        </is>
+      </c>
+      <c r="X819" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y819" s="2" t="inlineStr"/>
+      <c r="Z819" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA819" s="2" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="B820" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="C820" s="2" t="inlineStr">
+        <is>
+          <t>54996</t>
+        </is>
+      </c>
+      <c r="D820" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E820" s="2" t="inlineStr">
+        <is>
+          <t>Eisenberg an der Pinka</t>
+        </is>
+      </c>
+      <c r="F820" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Oberwart</t>
+        </is>
+      </c>
+      <c r="G820" s="2" t="inlineStr">
+        <is>
+          <t>1 Am Naturpark</t>
+        </is>
+      </c>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="I820" s="2" t="inlineStr">
+        <is>
+          <t>https://vinothek.eisenberg.at</t>
+        </is>
+      </c>
+      <c r="J820" s="2" t="inlineStr"/>
+      <c r="K820" s="2" t="inlineStr"/>
+      <c r="L820" s="2" t="inlineStr"/>
+      <c r="M820" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N820" s="2" t="inlineStr">
+        <is>
+          <t>wein@eisenberg.at</t>
+        </is>
+      </c>
+      <c r="O820" s="2" t="inlineStr">
+        <is>
+          <t>+43 3365 2666</t>
+        </is>
+      </c>
+      <c r="P820" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q820" s="2" t="inlineStr"/>
+      <c r="R820" s="2" t="inlineStr"/>
+      <c r="S820" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinothekeisenberg/</t>
+        </is>
+      </c>
+      <c r="T820" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinothek_eisenberg/</t>
+        </is>
+      </c>
+      <c r="U820" s="2" t="inlineStr"/>
+      <c r="V820" s="2" t="inlineStr"/>
+      <c r="W820" s="2" t="inlineStr"/>
+      <c r="X820" s="2" t="inlineStr"/>
+      <c r="Y820" s="2" t="inlineStr"/>
+      <c r="Z820" s="2" t="inlineStr"/>
+      <c r="AA820" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA820"/>
+  <dimension ref="A1:AA840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -81431,6 +81431,1990 @@
       <c r="Z820" s="2" t="inlineStr"/>
       <c r="AA820" s="2" t="inlineStr"/>
     </row>
+    <row r="821">
+      <c r="A821" s="2" t="inlineStr">
+        <is>
+          <t>Mk Weinothek Og</t>
+        </is>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>Mk Weinothek Og</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="inlineStr">
+        <is>
+          <t>28646</t>
+        </is>
+      </c>
+      <c r="D821" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Marein-Feistritz</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>28 Dorfstraße</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="I821" s="2" t="inlineStr">
+        <is>
+          <t>https://www.weinothek.at</t>
+        </is>
+      </c>
+      <c r="J821" s="2" t="inlineStr"/>
+      <c r="K821" s="2" t="inlineStr"/>
+      <c r="L821" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M821" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N821" s="2" t="inlineStr">
+        <is>
+          <t>info@weinothek.at</t>
+        </is>
+      </c>
+      <c r="O821" s="2" t="inlineStr"/>
+      <c r="P821" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q821" s="2" t="inlineStr">
+        <is>
+          <t>FN400514t</t>
+        </is>
+      </c>
+      <c r="R821" s="2" t="inlineStr"/>
+      <c r="S821" s="2" t="inlineStr"/>
+      <c r="T821" s="2" t="inlineStr"/>
+      <c r="U821" s="2" t="inlineStr"/>
+      <c r="V821" s="2" t="inlineStr"/>
+      <c r="W821" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Mossauer</t>
+        </is>
+      </c>
+      <c r="X821" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y821" s="2" t="inlineStr"/>
+      <c r="Z821" s="2" t="inlineStr"/>
+      <c r="AA821" s="2" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandel Fritz</t>
+        </is>
+      </c>
+      <c r="B822" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandel Fritz</t>
+        </is>
+      </c>
+      <c r="C822" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D822" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E822" s="2" t="inlineStr">
+        <is>
+          <t>Wörgl</t>
+        </is>
+      </c>
+      <c r="F822" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>2b Poststraße</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="I822" s="2" t="inlineStr">
+        <is>
+          <t>http://weinfreunde.at</t>
+        </is>
+      </c>
+      <c r="J822" s="2" t="inlineStr"/>
+      <c r="K822" s="2" t="inlineStr"/>
+      <c r="L822" s="2" t="inlineStr"/>
+      <c r="M822" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N822" s="2" t="inlineStr">
+        <is>
+          <t>r.fritz@tirol.com</t>
+        </is>
+      </c>
+      <c r="O822" s="2" t="inlineStr"/>
+      <c r="P822" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q822" s="2" t="inlineStr"/>
+      <c r="R822" s="2" t="inlineStr"/>
+      <c r="S822" s="2" t="inlineStr"/>
+      <c r="T822" s="2" t="inlineStr"/>
+      <c r="U822" s="2" t="inlineStr"/>
+      <c r="V822" s="2" t="inlineStr"/>
+      <c r="W822" s="2" t="inlineStr">
+        <is>
+          <t>Reinhard Fritz</t>
+        </is>
+      </c>
+      <c r="X822" s="2" t="inlineStr">
+        <is>
+          <t>Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y822" s="2" t="inlineStr"/>
+      <c r="Z822" s="2" t="inlineStr"/>
+      <c r="AA822" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reinhard-fritz-9bb4bb8a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="2" t="inlineStr">
+        <is>
+          <t>Markus Emmerich Friedl</t>
+        </is>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>Markus Emmerich Friedl</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D823" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="inlineStr">
+        <is>
+          <t>Draßmarkt</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>15 Haselbrunn</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="I823" s="2" t="inlineStr">
+        <is>
+          <t>https://weinfachhandel.at</t>
+        </is>
+      </c>
+      <c r="J823" s="2" t="inlineStr"/>
+      <c r="K823" s="2" t="inlineStr"/>
+      <c r="L823" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M823" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N823" s="2" t="inlineStr">
+        <is>
+          <t>office@weinfachhandel.at</t>
+        </is>
+      </c>
+      <c r="O823" s="2" t="inlineStr"/>
+      <c r="P823" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q823" s="2" t="inlineStr">
+        <is>
+          <t>ATU56640629</t>
+        </is>
+      </c>
+      <c r="R823" s="2" t="inlineStr"/>
+      <c r="S823" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bacchuskeller-vinothek-647673035250938</t>
+        </is>
+      </c>
+      <c r="T823" s="2" t="inlineStr"/>
+      <c r="U823" s="2" t="inlineStr"/>
+      <c r="V823" s="2" t="inlineStr"/>
+      <c r="W823" s="2" t="inlineStr">
+        <is>
+          <t>Markus Friedl</t>
+        </is>
+      </c>
+      <c r="X823" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y823" s="2" t="inlineStr"/>
+      <c r="Z823" s="2" t="inlineStr"/>
+      <c r="AA823" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/weinfachhandel-und-vinothek-friedl-markus-ehem-bacchuskeller-9637b112a/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2" t="inlineStr">
+        <is>
+          <t>Weine Englitsch</t>
+        </is>
+      </c>
+      <c r="B824" s="2" t="inlineStr">
+        <is>
+          <t>Weine Englitsch</t>
+        </is>
+      </c>
+      <c r="C824" s="2" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="D824" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E824" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F824" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G824" s="2" t="inlineStr">
+        <is>
+          <t>41 Gablenzgasse</t>
+        </is>
+      </c>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="I824" s="2" t="inlineStr">
+        <is>
+          <t>https://englitsch.com</t>
+        </is>
+      </c>
+      <c r="J824" s="2" t="inlineStr"/>
+      <c r="K824" s="2" t="inlineStr"/>
+      <c r="L824" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M824" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N824" s="2" t="inlineStr">
+        <is>
+          <t>info@englitsch.com</t>
+        </is>
+      </c>
+      <c r="O824" s="2" t="inlineStr"/>
+      <c r="P824" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q824" s="2" t="inlineStr">
+        <is>
+          <t>ATU38006901</t>
+        </is>
+      </c>
+      <c r="R824" s="2" t="inlineStr"/>
+      <c r="S824" s="2" t="inlineStr"/>
+      <c r="T824" s="2" t="inlineStr"/>
+      <c r="U824" s="2" t="inlineStr"/>
+      <c r="V824" s="2" t="inlineStr"/>
+      <c r="W824" s="2" t="inlineStr"/>
+      <c r="X824" s="2" t="inlineStr"/>
+      <c r="Y824" s="2" t="inlineStr"/>
+      <c r="Z824" s="2" t="inlineStr"/>
+      <c r="AA824" s="2" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandlung Kohlbacher</t>
+        </is>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandlung Kohlbacher</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="inlineStr">
+        <is>
+          <t>Graz</t>
+        </is>
+      </c>
+      <c r="F825" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>3 Leonhardstraße</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="I825" s="2" t="inlineStr">
+        <is>
+          <t>https://weinhandel-kohlbacher.at</t>
+        </is>
+      </c>
+      <c r="J825" s="2" t="inlineStr"/>
+      <c r="K825" s="2" t="inlineStr"/>
+      <c r="L825" s="2" t="inlineStr"/>
+      <c r="M825" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N825" s="2" t="inlineStr">
+        <is>
+          <t>office@weinhandel-kohlbacher.at</t>
+        </is>
+      </c>
+      <c r="O825" s="2" t="inlineStr">
+        <is>
+          <t>+43 316 319431</t>
+        </is>
+      </c>
+      <c r="P825" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q825" s="2" t="inlineStr"/>
+      <c r="R825" s="2" t="inlineStr"/>
+      <c r="S825" s="2" t="inlineStr"/>
+      <c r="T825" s="2" t="inlineStr"/>
+      <c r="U825" s="2" t="inlineStr"/>
+      <c r="V825" s="2" t="inlineStr"/>
+      <c r="W825" s="2" t="inlineStr">
+        <is>
+          <t>Anton Kohlbacher</t>
+        </is>
+      </c>
+      <c r="X825" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y825" s="2" t="inlineStr"/>
+      <c r="Z825" s="2" t="inlineStr"/>
+      <c r="AA825" s="2" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Weinkult E.u.</t>
+        </is>
+      </c>
+      <c r="B826" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Weinkult E.u.</t>
+        </is>
+      </c>
+      <c r="C826" s="2" t="inlineStr">
+        <is>
+          <t>20409</t>
+        </is>
+      </c>
+      <c r="D826" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E826" s="2" t="inlineStr">
+        <is>
+          <t>Guntramsdorf</t>
+        </is>
+      </c>
+      <c r="F826" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Mödling</t>
+        </is>
+      </c>
+      <c r="G826" s="2" t="inlineStr">
+        <is>
+          <t>16 Josef-Lanner-Straße</t>
+        </is>
+      </c>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="I826" s="2" t="inlineStr">
+        <is>
+          <t>https://weinkult.at</t>
+        </is>
+      </c>
+      <c r="J826" s="2" t="inlineStr"/>
+      <c r="K826" s="2" t="inlineStr"/>
+      <c r="L826" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M826" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N826" s="2" t="inlineStr">
+        <is>
+          <t>office@weinkult.at</t>
+        </is>
+      </c>
+      <c r="O826" s="2" t="inlineStr"/>
+      <c r="P826" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q826" s="2" t="inlineStr">
+        <is>
+          <t>FN264999f</t>
+        </is>
+      </c>
+      <c r="R826" s="2" t="inlineStr"/>
+      <c r="S826" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinothek-WeinKult-459948980864240/</t>
+        </is>
+      </c>
+      <c r="T826" s="2" t="inlineStr"/>
+      <c r="U826" s="2" t="inlineStr"/>
+      <c r="V826" s="2" t="inlineStr"/>
+      <c r="W826" s="2" t="inlineStr">
+        <is>
+          <t>Gerhard Antreich</t>
+        </is>
+      </c>
+      <c r="X826" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y826" s="2" t="inlineStr"/>
+      <c r="Z826" s="2" t="inlineStr"/>
+      <c r="AA826" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gerhard-antreich-8812aa114/</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2" t="inlineStr">
+        <is>
+          <t>Speckbacher Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>Speckbacher Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="inlineStr">
+        <is>
+          <t>30873</t>
+        </is>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>Reutte</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>15 Großfeldstraße</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="I827" s="2" t="inlineStr">
+        <is>
+          <t>https://www.speckbacher.at</t>
+        </is>
+      </c>
+      <c r="J827" s="2" t="inlineStr"/>
+      <c r="K827" s="2" t="inlineStr"/>
+      <c r="L827" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M827" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N827" s="2" t="inlineStr">
+        <is>
+          <t>kundenservice@speckbacher.at</t>
+        </is>
+      </c>
+      <c r="O827" s="2" t="inlineStr">
+        <is>
+          <t>+43 5672 62217</t>
+        </is>
+      </c>
+      <c r="P827" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="Q827" s="2" t="inlineStr">
+        <is>
+          <t>FN415717z</t>
+        </is>
+      </c>
+      <c r="R827" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eurogast-speckbacher/</t>
+        </is>
+      </c>
+      <c r="S827" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/speckbacher.at/</t>
+        </is>
+      </c>
+      <c r="T827" s="2" t="inlineStr"/>
+      <c r="U827" s="2" t="inlineStr"/>
+      <c r="V827" s="2" t="inlineStr"/>
+      <c r="W827" s="2" t="inlineStr">
+        <is>
+          <t>Peter Speckbacher</t>
+        </is>
+      </c>
+      <c r="X827" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="Y827" s="2" t="inlineStr"/>
+      <c r="Z827" s="2" t="inlineStr"/>
+      <c r="AA827" s="2" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="2" t="inlineStr">
+        <is>
+          <t>Vini Mascoli Kg</t>
+        </is>
+      </c>
+      <c r="B828" s="2" t="inlineStr">
+        <is>
+          <t>Vini Mascoli Kg</t>
+        </is>
+      </c>
+      <c r="C828" s="2" t="inlineStr">
+        <is>
+          <t>25324</t>
+        </is>
+      </c>
+      <c r="D828" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E828" s="2" t="inlineStr">
+        <is>
+          <t>Klaus</t>
+        </is>
+      </c>
+      <c r="F828" s="2" t="inlineStr">
+        <is>
+          <t>Vorarlberg</t>
+        </is>
+      </c>
+      <c r="G828" s="2" t="inlineStr">
+        <is>
+          <t>17 Treietstraße</t>
+        </is>
+      </c>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="I828" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amicidelvino.at</t>
+        </is>
+      </c>
+      <c r="J828" s="2" t="inlineStr"/>
+      <c r="K828" s="2" t="inlineStr"/>
+      <c r="L828" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M828" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N828" s="2" t="inlineStr">
+        <is>
+          <t>shop@amicidelvino.at</t>
+        </is>
+      </c>
+      <c r="O828" s="2" t="inlineStr"/>
+      <c r="P828" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q828" s="2" t="inlineStr">
+        <is>
+          <t>FN281204k</t>
+        </is>
+      </c>
+      <c r="R828" s="2" t="inlineStr"/>
+      <c r="S828" s="2" t="inlineStr"/>
+      <c r="T828" s="2" t="inlineStr"/>
+      <c r="U828" s="2" t="inlineStr"/>
+      <c r="V828" s="2" t="inlineStr"/>
+      <c r="W828" s="2" t="inlineStr">
+        <is>
+          <t>Markus Ender</t>
+        </is>
+      </c>
+      <c r="X828" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y828" s="2" t="inlineStr"/>
+      <c r="Z828" s="2" t="inlineStr"/>
+      <c r="AA828" s="2" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="2" t="inlineStr">
+        <is>
+          <t>Markus Saletz</t>
+        </is>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>Markus Saletz</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="inlineStr">
+        <is>
+          <t>54968</t>
+        </is>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>Gemeinde Reutte</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Reutte</t>
+        </is>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>24 Untermarkt</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="I829" s="2" t="inlineStr">
+        <is>
+          <t>https://www.markus-saletz.at</t>
+        </is>
+      </c>
+      <c r="J829" s="2" t="inlineStr"/>
+      <c r="K829" s="2" t="inlineStr"/>
+      <c r="L829" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M829" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N829" s="2" t="inlineStr">
+        <is>
+          <t>welcome@markus-saletz.at</t>
+        </is>
+      </c>
+      <c r="O829" s="2" t="inlineStr"/>
+      <c r="P829" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q829" s="2" t="inlineStr">
+        <is>
+          <t>ATU68531724</t>
+        </is>
+      </c>
+      <c r="R829" s="2" t="inlineStr"/>
+      <c r="S829" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Markus-Saletz-Lieblingsweine-1588202668063142/</t>
+        </is>
+      </c>
+      <c r="T829" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/markus_saletz_lieblingsweine/</t>
+        </is>
+      </c>
+      <c r="U829" s="2" t="inlineStr"/>
+      <c r="V829" s="2" t="inlineStr"/>
+      <c r="W829" s="2" t="inlineStr">
+        <is>
+          <t>Markus Saletz</t>
+        </is>
+      </c>
+      <c r="X829" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y829" s="2" t="inlineStr"/>
+      <c r="Z829" s="2" t="inlineStr"/>
+      <c r="AA829" s="2" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="2" t="inlineStr">
+        <is>
+          <t>A.b. Bittermann Restaurations Gmbh</t>
+        </is>
+      </c>
+      <c r="B830" s="2" t="inlineStr">
+        <is>
+          <t>A.b. Bittermann Restaurations Gmbh</t>
+        </is>
+      </c>
+      <c r="C830" s="2" t="inlineStr">
+        <is>
+          <t>20419</t>
+        </is>
+      </c>
+      <c r="D830" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E830" s="2" t="inlineStr">
+        <is>
+          <t>Göttlesbrunn</t>
+        </is>
+      </c>
+      <c r="F830" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Bruck an der Leitha</t>
+        </is>
+      </c>
+      <c r="G830" s="2" t="inlineStr">
+        <is>
+          <t>1 Abt-Bruno-Heinrich-Platz</t>
+        </is>
+      </c>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="I830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adi-bittermann.at</t>
+        </is>
+      </c>
+      <c r="J830" s="2" t="inlineStr"/>
+      <c r="K830" s="2" t="inlineStr"/>
+      <c r="L830" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M830" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N830" s="2" t="inlineStr">
+        <is>
+          <t>info@adi-bittermann.at</t>
+        </is>
+      </c>
+      <c r="O830" s="2" t="inlineStr">
+        <is>
+          <t>+43 2162 81155</t>
+        </is>
+      </c>
+      <c r="P830" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q830" s="2" t="inlineStr">
+        <is>
+          <t>FN246954v</t>
+        </is>
+      </c>
+      <c r="R830" s="2" t="inlineStr"/>
+      <c r="S830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bittermann-vinarium-göttlesbrunn-179273462110267/</t>
+        </is>
+      </c>
+      <c r="T830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bittermannadi/</t>
+        </is>
+      </c>
+      <c r="U830" s="2" t="inlineStr"/>
+      <c r="V830" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@adibittermann5167/</t>
+        </is>
+      </c>
+      <c r="W830" s="2" t="inlineStr">
+        <is>
+          <t>Adi Bittermann</t>
+        </is>
+      </c>
+      <c r="X830" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y830" s="2" t="inlineStr"/>
+      <c r="Z830" s="2" t="inlineStr"/>
+      <c r="AA830" s="2" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="2" t="inlineStr">
+        <is>
+          <t>Hieber Consulting Gmbh</t>
+        </is>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>Hieber Consulting Gmbh</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D831" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F831" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>1 Schaukalgasse</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="I831" s="2" t="inlineStr">
+        <is>
+          <t>https://hieber.at</t>
+        </is>
+      </c>
+      <c r="J831" s="2" t="inlineStr"/>
+      <c r="K831" s="2" t="inlineStr"/>
+      <c r="L831" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M831" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N831" s="2" t="inlineStr">
+        <is>
+          <t>trade@hieber.at</t>
+        </is>
+      </c>
+      <c r="O831" s="2" t="inlineStr"/>
+      <c r="P831" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q831" s="2" t="inlineStr">
+        <is>
+          <t>FN265189i</t>
+        </is>
+      </c>
+      <c r="R831" s="2" t="inlineStr"/>
+      <c r="S831" s="2" t="inlineStr"/>
+      <c r="T831" s="2" t="inlineStr"/>
+      <c r="U831" s="2" t="inlineStr"/>
+      <c r="V831" s="2" t="inlineStr"/>
+      <c r="W831" s="2" t="inlineStr">
+        <is>
+          <t>Stefan Hieber</t>
+        </is>
+      </c>
+      <c r="X831" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y831" s="2" t="inlineStr"/>
+      <c r="Z831" s="2" t="inlineStr"/>
+      <c r="AA831" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefan-hieber-0b93a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2" t="inlineStr">
+        <is>
+          <t>Christian Grasl</t>
+        </is>
+      </c>
+      <c r="B832" s="2" t="inlineStr">
+        <is>
+          <t>Christian Grasl</t>
+        </is>
+      </c>
+      <c r="C832" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="D832" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E832" s="2" t="inlineStr">
+        <is>
+          <t>Wilhelmsburg</t>
+        </is>
+      </c>
+      <c r="F832" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G832" s="2" t="inlineStr">
+        <is>
+          <t>28 Anzengruberstraße</t>
+        </is>
+      </c>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="I832" s="2" t="inlineStr">
+        <is>
+          <t>http://weinkeller-online.at</t>
+        </is>
+      </c>
+      <c r="J832" s="2" t="inlineStr"/>
+      <c r="K832" s="2" t="inlineStr"/>
+      <c r="L832" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M832" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N832" s="2" t="inlineStr">
+        <is>
+          <t>office@weinkeller-online.at</t>
+        </is>
+      </c>
+      <c r="O832" s="2" t="inlineStr">
+        <is>
+          <t>+43 2746 2807</t>
+        </is>
+      </c>
+      <c r="P832" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q832" s="2" t="inlineStr">
+        <is>
+          <t>ATU54210802</t>
+        </is>
+      </c>
+      <c r="R832" s="2" t="inlineStr"/>
+      <c r="S832" s="2" t="inlineStr"/>
+      <c r="T832" s="2" t="inlineStr"/>
+      <c r="U832" s="2" t="inlineStr"/>
+      <c r="V832" s="2" t="inlineStr"/>
+      <c r="W832" s="2" t="inlineStr">
+        <is>
+          <t>Christian Grasl</t>
+        </is>
+      </c>
+      <c r="X832" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y832" s="2" t="inlineStr"/>
+      <c r="Z832" s="2" t="inlineStr"/>
+      <c r="AA832" s="2" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="inlineStr">
+        <is>
+          <t>53045</t>
+        </is>
+      </c>
+      <c r="D833" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Innsbruck-Land</t>
+        </is>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>20 Auweg</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="I833" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="J833" s="2" t="inlineStr"/>
+      <c r="K833" s="2" t="inlineStr"/>
+      <c r="L833" s="2" t="inlineStr"/>
+      <c r="M833" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N833" s="2" t="inlineStr">
+        <is>
+          <t>marco@beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="O833" s="2" t="inlineStr">
+        <is>
+          <t>+43 5224 22023203</t>
+        </is>
+      </c>
+      <c r="P833" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q833" s="2" t="inlineStr"/>
+      <c r="R833" s="2" t="inlineStr"/>
+      <c r="S833" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/beveragecompany.at/</t>
+        </is>
+      </c>
+      <c r="T833" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beveragecompany/</t>
+        </is>
+      </c>
+      <c r="U833" s="2" t="inlineStr"/>
+      <c r="V833" s="2" t="inlineStr"/>
+      <c r="W833" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Weingerl</t>
+        </is>
+      </c>
+      <c r="X833" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y833" s="2" t="inlineStr"/>
+      <c r="Z833" s="2" t="inlineStr"/>
+      <c r="AA833" s="2" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>53045</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Innsbruck-Land</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr">
+        <is>
+          <t>20 Auweg</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="I834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="J834" s="2" t="inlineStr"/>
+      <c r="K834" s="2" t="inlineStr"/>
+      <c r="L834" s="2" t="inlineStr"/>
+      <c r="M834" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N834" s="2" t="inlineStr">
+        <is>
+          <t>marco@beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="O834" s="2" t="inlineStr">
+        <is>
+          <t>+43 5224 22023203</t>
+        </is>
+      </c>
+      <c r="P834" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q834" s="2" t="inlineStr"/>
+      <c r="R834" s="2" t="inlineStr"/>
+      <c r="S834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/beveragecompany.at/</t>
+        </is>
+      </c>
+      <c r="T834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beveragecompany/</t>
+        </is>
+      </c>
+      <c r="U834" s="2" t="inlineStr"/>
+      <c r="V834" s="2" t="inlineStr"/>
+      <c r="W834" s="2" t="inlineStr">
+        <is>
+          <t>Marco Bachler</t>
+        </is>
+      </c>
+      <c r="X834" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y834" s="2" t="inlineStr"/>
+      <c r="Z834" s="2" t="inlineStr"/>
+      <c r="AA834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-bachler-688a2067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="inlineStr">
+        <is>
+          <t>Neun Weine Gmbh</t>
+        </is>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>Neun Weine Gmbh</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>61544</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>Neutal</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Oberpullendorf</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>7 Werner von Siemens-Straße</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="I835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neunweine.at, https://www.neunweine.de</t>
+        </is>
+      </c>
+      <c r="J835" s="2" t="inlineStr"/>
+      <c r="K835" s="2" t="inlineStr"/>
+      <c r="L835" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M835" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N835" s="2" t="inlineStr">
+        <is>
+          <t>michael@neunweine.at</t>
+        </is>
+      </c>
+      <c r="O835" s="2" t="inlineStr">
+        <is>
+          <t>+43 720 3030505099</t>
+        </is>
+      </c>
+      <c r="P835" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q835" s="2" t="inlineStr">
+        <is>
+          <t>FN432466f</t>
+        </is>
+      </c>
+      <c r="R835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neun-weine/</t>
+        </is>
+      </c>
+      <c r="S835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/neunweine/</t>
+        </is>
+      </c>
+      <c r="T835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neunweine/</t>
+        </is>
+      </c>
+      <c r="U835" s="2" t="inlineStr"/>
+      <c r="V835" s="2" t="inlineStr"/>
+      <c r="W835" s="2" t="inlineStr">
+        <is>
+          <t>Michael Pruenner</t>
+        </is>
+      </c>
+      <c r="X835" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y835" s="2" t="inlineStr"/>
+      <c r="Z835" s="2" t="inlineStr"/>
+      <c r="AA835" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/michael-pruenner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I836" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J836" s="2" t="inlineStr"/>
+      <c r="K836" s="2" t="inlineStr"/>
+      <c r="L836" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M836" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N836" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O836" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P836" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q836" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R836" s="2" t="inlineStr"/>
+      <c r="S836" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T836" s="2" t="inlineStr"/>
+      <c r="U836" s="2" t="inlineStr"/>
+      <c r="V836" s="2" t="inlineStr"/>
+      <c r="W836" s="2" t="inlineStr">
+        <is>
+          <t>Gerhard Kracher</t>
+        </is>
+      </c>
+      <c r="X836" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y836" s="2" t="inlineStr"/>
+      <c r="Z836" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA836" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gerhard-kracher-5568b1149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I837" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J837" s="2" t="inlineStr"/>
+      <c r="K837" s="2" t="inlineStr"/>
+      <c r="L837" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M837" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N837" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O837" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P837" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q837" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R837" s="2" t="inlineStr"/>
+      <c r="S837" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T837" s="2" t="inlineStr"/>
+      <c r="U837" s="2" t="inlineStr"/>
+      <c r="V837" s="2" t="inlineStr"/>
+      <c r="W837" s="2" t="inlineStr">
+        <is>
+          <t>Hans Martin</t>
+        </is>
+      </c>
+      <c r="X837" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Manager/ Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y837" s="2" t="inlineStr"/>
+      <c r="Z837" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I838" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J838" s="2" t="inlineStr"/>
+      <c r="K838" s="2" t="inlineStr"/>
+      <c r="L838" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M838" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N838" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O838" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P838" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q838" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R838" s="2" t="inlineStr"/>
+      <c r="S838" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T838" s="2" t="inlineStr"/>
+      <c r="U838" s="2" t="inlineStr"/>
+      <c r="V838" s="2" t="inlineStr"/>
+      <c r="W838" s="2" t="inlineStr">
+        <is>
+          <t>Yvonne Kracher</t>
+        </is>
+      </c>
+      <c r="X838" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Sales</t>
+        </is>
+      </c>
+      <c r="Y838" s="2" t="inlineStr"/>
+      <c r="Z838" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA838" s="2" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I839" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J839" s="2" t="inlineStr"/>
+      <c r="K839" s="2" t="inlineStr"/>
+      <c r="L839" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M839" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N839" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O839" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P839" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q839" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R839" s="2" t="inlineStr"/>
+      <c r="S839" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T839" s="2" t="inlineStr"/>
+      <c r="U839" s="2" t="inlineStr"/>
+      <c r="V839" s="2" t="inlineStr"/>
+      <c r="W839" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Wolf</t>
+        </is>
+      </c>
+      <c r="X839" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y839" s="2" t="inlineStr"/>
+      <c r="Z839" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>54996</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch Schützen-Eisenberg</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>1 Am Naturpark</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="I840" s="2" t="inlineStr">
+        <is>
+          <t>https://vinothek.eisenberg.at</t>
+        </is>
+      </c>
+      <c r="J840" s="2" t="inlineStr"/>
+      <c r="K840" s="2" t="inlineStr"/>
+      <c r="L840" s="2" t="inlineStr"/>
+      <c r="M840" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N840" s="2" t="inlineStr">
+        <is>
+          <t>wein@eisenberg.at</t>
+        </is>
+      </c>
+      <c r="O840" s="2" t="inlineStr">
+        <is>
+          <t>+43 3365 2666</t>
+        </is>
+      </c>
+      <c r="P840" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q840" s="2" t="inlineStr"/>
+      <c r="R840" s="2" t="inlineStr"/>
+      <c r="S840" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinothekeisenberg/</t>
+        </is>
+      </c>
+      <c r="T840" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinothek_eisenberg/</t>
+        </is>
+      </c>
+      <c r="U840" s="2" t="inlineStr"/>
+      <c r="V840" s="2" t="inlineStr"/>
+      <c r="W840" s="2" t="inlineStr"/>
+      <c r="X840" s="2" t="inlineStr"/>
+      <c r="Y840" s="2" t="inlineStr"/>
+      <c r="Z840" s="2" t="inlineStr"/>
+      <c r="AA840" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA840"/>
+  <dimension ref="A1:AA865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -83415,6 +83415,2483 @@
       <c r="Z840" s="2" t="inlineStr"/>
       <c r="AA840" s="2" t="inlineStr"/>
     </row>
+    <row r="841">
+      <c r="A841" s="2" t="inlineStr">
+        <is>
+          <t>Weinhaus Wakolbinger Gmbh</t>
+        </is>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>Weinhaus Wakolbinger Gmbh</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>Lichtenberg</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>Upper Austria</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>14 Am Holzpoldlgut</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="I841" s="2" t="inlineStr">
+        <is>
+          <t>https://wakolbinger.at</t>
+        </is>
+      </c>
+      <c r="J841" s="2" t="inlineStr"/>
+      <c r="K841" s="2" t="inlineStr"/>
+      <c r="L841" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M841" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N841" s="2" t="inlineStr">
+        <is>
+          <t>weinhaus@wakolbinger.at</t>
+        </is>
+      </c>
+      <c r="O841" s="2" t="inlineStr">
+        <is>
+          <t>+43 7239 62280</t>
+        </is>
+      </c>
+      <c r="P841" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q841" s="2" t="inlineStr">
+        <is>
+          <t>FN261758p</t>
+        </is>
+      </c>
+      <c r="R841" s="2" t="inlineStr"/>
+      <c r="S841" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/weinhauswakolbinger.at</t>
+        </is>
+      </c>
+      <c r="T841" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weinhaus_wakolbinger/</t>
+        </is>
+      </c>
+      <c r="U841" s="2" t="inlineStr"/>
+      <c r="V841" s="2" t="inlineStr"/>
+      <c r="W841" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Wakolbinger</t>
+        </is>
+      </c>
+      <c r="X841" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y841" s="2" t="inlineStr"/>
+      <c r="Z841" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="inlineStr">
+        <is>
+          <t>Weinhaus Mag. Helmut Reischl E.u.</t>
+        </is>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>Weinhaus Mag. Helmut Reischl E.u.</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>Graz</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr">
+        <is>
+          <t>28a Petersgasse</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="I842" s="2" t="inlineStr">
+        <is>
+          <t>https://dergallier.at</t>
+        </is>
+      </c>
+      <c r="J842" s="2" t="inlineStr"/>
+      <c r="K842" s="2" t="inlineStr"/>
+      <c r="L842" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M842" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N842" s="2" t="inlineStr">
+        <is>
+          <t>dergallier@gmx.at</t>
+        </is>
+      </c>
+      <c r="O842" s="2" t="inlineStr"/>
+      <c r="P842" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q842" s="2" t="inlineStr">
+        <is>
+          <t>FN307124d</t>
+        </is>
+      </c>
+      <c r="R842" s="2" t="inlineStr"/>
+      <c r="S842" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/weinhaus-der-gallier-222245174480920</t>
+        </is>
+      </c>
+      <c r="T842" s="2" t="inlineStr"/>
+      <c r="U842" s="2" t="inlineStr"/>
+      <c r="V842" s="2" t="inlineStr"/>
+      <c r="W842" s="2" t="inlineStr">
+        <is>
+          <t>Reischl Helmut</t>
+        </is>
+      </c>
+      <c r="X842" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y842" s="2" t="inlineStr"/>
+      <c r="Z842" s="2" t="inlineStr"/>
+      <c r="AA842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="inlineStr">
+        <is>
+          <t>Vinorama Weinversandgesellschaft M.b.h.</t>
+        </is>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>Vinorama Weinversandgesellschaft M.b.h.</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>Wörgl</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>13 Wörgler Boden</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="I843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vinorama.at</t>
+        </is>
+      </c>
+      <c r="J843" s="2" t="inlineStr"/>
+      <c r="K843" s="2" t="inlineStr"/>
+      <c r="L843" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M843" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N843" s="2" t="inlineStr">
+        <is>
+          <t>info@vinorama.at</t>
+        </is>
+      </c>
+      <c r="O843" s="2" t="inlineStr">
+        <is>
+          <t>+43 50 220 500</t>
+        </is>
+      </c>
+      <c r="P843" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="Q843" s="2" t="inlineStr">
+        <is>
+          <t>FN44943v</t>
+        </is>
+      </c>
+      <c r="R843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinoramaweinversand/</t>
+        </is>
+      </c>
+      <c r="S843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinorama</t>
+        </is>
+      </c>
+      <c r="T843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinorama_at/</t>
+        </is>
+      </c>
+      <c r="U843" s="2" t="inlineStr"/>
+      <c r="V843" s="2" t="inlineStr"/>
+      <c r="W843" s="2" t="inlineStr">
+        <is>
+          <t>Christoph Morandell</t>
+        </is>
+      </c>
+      <c r="X843" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y843" s="2" t="inlineStr"/>
+      <c r="Z843" s="2" t="inlineStr"/>
+      <c r="AA843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="inlineStr">
+        <is>
+          <t>Deschka Weinbar Vinothek</t>
+        </is>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>Deschka Weinbar Vinothek</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>111 Schönbrunner Straße</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>1050</t>
+        </is>
+      </c>
+      <c r="I844" s="2" t="inlineStr">
+        <is>
+          <t>https://www.weindeschka.com</t>
+        </is>
+      </c>
+      <c r="J844" s="2" t="inlineStr"/>
+      <c r="K844" s="2" t="inlineStr"/>
+      <c r="L844" s="2" t="inlineStr"/>
+      <c r="M844" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N844" s="2" t="inlineStr">
+        <is>
+          <t>office@weindeschka.com</t>
+        </is>
+      </c>
+      <c r="O844" s="2" t="inlineStr"/>
+      <c r="P844" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q844" s="2" t="inlineStr"/>
+      <c r="R844" s="2" t="inlineStr"/>
+      <c r="S844" s="2" t="inlineStr"/>
+      <c r="T844" s="2" t="inlineStr"/>
+      <c r="U844" s="2" t="inlineStr"/>
+      <c r="V844" s="2" t="inlineStr"/>
+      <c r="W844" s="2" t="inlineStr"/>
+      <c r="X844" s="2" t="inlineStr"/>
+      <c r="Y844" s="2" t="inlineStr"/>
+      <c r="Z844" s="2" t="inlineStr"/>
+      <c r="AA844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="inlineStr">
+        <is>
+          <t>Winetaste Kg</t>
+        </is>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>Winetaste Kg</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>54946</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>Kitzbühel</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>Tirol</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>39 Sonngrub</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="I845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.weinherz.at</t>
+        </is>
+      </c>
+      <c r="J845" s="2" t="inlineStr"/>
+      <c r="K845" s="2" t="inlineStr"/>
+      <c r="L845" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M845" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N845" s="2" t="inlineStr">
+        <is>
+          <t>info@weinherz.at</t>
+        </is>
+      </c>
+      <c r="O845" s="2" t="inlineStr"/>
+      <c r="P845" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q845" s="2" t="inlineStr">
+        <is>
+          <t>FN521481i</t>
+        </is>
+      </c>
+      <c r="R845" s="2" t="inlineStr"/>
+      <c r="S845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/weinherz</t>
+        </is>
+      </c>
+      <c r="T845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weinherz.kitzbuehel/</t>
+        </is>
+      </c>
+      <c r="U845" s="2" t="inlineStr"/>
+      <c r="V845" s="2" t="inlineStr"/>
+      <c r="W845" s="2" t="inlineStr">
+        <is>
+          <t>Yvonne C.</t>
+        </is>
+      </c>
+      <c r="X845" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y845" s="2" t="inlineStr"/>
+      <c r="Z845" s="2" t="inlineStr"/>
+      <c r="AA845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="inlineStr">
+        <is>
+          <t>Mk Weinothek Og</t>
+        </is>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>Mk Weinothek Og</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>28646</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Marein-Feistritz</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>28 Dorfstraße</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>8733</t>
+        </is>
+      </c>
+      <c r="I846" s="2" t="inlineStr">
+        <is>
+          <t>https://www.weinothek.at</t>
+        </is>
+      </c>
+      <c r="J846" s="2" t="inlineStr"/>
+      <c r="K846" s="2" t="inlineStr"/>
+      <c r="L846" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M846" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N846" s="2" t="inlineStr">
+        <is>
+          <t>info@weinothek.at</t>
+        </is>
+      </c>
+      <c r="O846" s="2" t="inlineStr"/>
+      <c r="P846" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q846" s="2" t="inlineStr">
+        <is>
+          <t>FN400514t</t>
+        </is>
+      </c>
+      <c r="R846" s="2" t="inlineStr"/>
+      <c r="S846" s="2" t="inlineStr"/>
+      <c r="T846" s="2" t="inlineStr"/>
+      <c r="U846" s="2" t="inlineStr"/>
+      <c r="V846" s="2" t="inlineStr"/>
+      <c r="W846" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Mossauer</t>
+        </is>
+      </c>
+      <c r="X846" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y846" s="2" t="inlineStr"/>
+      <c r="Z846" s="2" t="inlineStr"/>
+      <c r="AA846" s="2" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandel Fritz</t>
+        </is>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandel Fritz</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>Wörgl</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>2b Poststraße</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="I847" s="2" t="inlineStr">
+        <is>
+          <t>http://weinfreunde.at</t>
+        </is>
+      </c>
+      <c r="J847" s="2" t="inlineStr"/>
+      <c r="K847" s="2" t="inlineStr"/>
+      <c r="L847" s="2" t="inlineStr"/>
+      <c r="M847" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N847" s="2" t="inlineStr">
+        <is>
+          <t>r.fritz@tirol.com</t>
+        </is>
+      </c>
+      <c r="O847" s="2" t="inlineStr"/>
+      <c r="P847" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q847" s="2" t="inlineStr"/>
+      <c r="R847" s="2" t="inlineStr"/>
+      <c r="S847" s="2" t="inlineStr"/>
+      <c r="T847" s="2" t="inlineStr"/>
+      <c r="U847" s="2" t="inlineStr"/>
+      <c r="V847" s="2" t="inlineStr"/>
+      <c r="W847" s="2" t="inlineStr">
+        <is>
+          <t>Reinhard Fritz</t>
+        </is>
+      </c>
+      <c r="X847" s="2" t="inlineStr">
+        <is>
+          <t>Wine Merchant</t>
+        </is>
+      </c>
+      <c r="Y847" s="2" t="inlineStr"/>
+      <c r="Z847" s="2" t="inlineStr"/>
+      <c r="AA847" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/reinhard-fritz-9bb4bb8a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="inlineStr">
+        <is>
+          <t>Markus Emmerich Friedl</t>
+        </is>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>Markus Emmerich Friedl</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>Draßmarkt</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>15 Haselbrunn</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="I848" s="2" t="inlineStr">
+        <is>
+          <t>https://weinfachhandel.at</t>
+        </is>
+      </c>
+      <c r="J848" s="2" t="inlineStr"/>
+      <c r="K848" s="2" t="inlineStr"/>
+      <c r="L848" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M848" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N848" s="2" t="inlineStr">
+        <is>
+          <t>office@weinfachhandel.at</t>
+        </is>
+      </c>
+      <c r="O848" s="2" t="inlineStr"/>
+      <c r="P848" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q848" s="2" t="inlineStr">
+        <is>
+          <t>ATU56640629</t>
+        </is>
+      </c>
+      <c r="R848" s="2" t="inlineStr"/>
+      <c r="S848" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bacchuskeller-vinothek-647673035250938</t>
+        </is>
+      </c>
+      <c r="T848" s="2" t="inlineStr"/>
+      <c r="U848" s="2" t="inlineStr"/>
+      <c r="V848" s="2" t="inlineStr"/>
+      <c r="W848" s="2" t="inlineStr">
+        <is>
+          <t>Markus Friedl</t>
+        </is>
+      </c>
+      <c r="X848" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y848" s="2" t="inlineStr"/>
+      <c r="Z848" s="2" t="inlineStr"/>
+      <c r="AA848" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/weinfachhandel-und-vinothek-friedl-markus-ehem-bacchuskeller-9637b112a/?originalSubdomain=at</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="inlineStr">
+        <is>
+          <t>Weine Englitsch</t>
+        </is>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>Weine Englitsch</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>41 Gablenzgasse</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="I849" s="2" t="inlineStr">
+        <is>
+          <t>https://englitsch.com</t>
+        </is>
+      </c>
+      <c r="J849" s="2" t="inlineStr"/>
+      <c r="K849" s="2" t="inlineStr"/>
+      <c r="L849" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M849" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N849" s="2" t="inlineStr">
+        <is>
+          <t>info@englitsch.com</t>
+        </is>
+      </c>
+      <c r="O849" s="2" t="inlineStr"/>
+      <c r="P849" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q849" s="2" t="inlineStr">
+        <is>
+          <t>ATU38006901</t>
+        </is>
+      </c>
+      <c r="R849" s="2" t="inlineStr"/>
+      <c r="S849" s="2" t="inlineStr"/>
+      <c r="T849" s="2" t="inlineStr"/>
+      <c r="U849" s="2" t="inlineStr"/>
+      <c r="V849" s="2" t="inlineStr"/>
+      <c r="W849" s="2" t="inlineStr"/>
+      <c r="X849" s="2" t="inlineStr"/>
+      <c r="Y849" s="2" t="inlineStr"/>
+      <c r="Z849" s="2" t="inlineStr"/>
+      <c r="AA849" s="2" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandlung Kohlbacher</t>
+        </is>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>Weinhandlung Kohlbacher</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>Graz</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>Styria</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>3 Leonhardstraße</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="I850" s="2" t="inlineStr">
+        <is>
+          <t>https://weinhandel-kohlbacher.at</t>
+        </is>
+      </c>
+      <c r="J850" s="2" t="inlineStr"/>
+      <c r="K850" s="2" t="inlineStr"/>
+      <c r="L850" s="2" t="inlineStr"/>
+      <c r="M850" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N850" s="2" t="inlineStr">
+        <is>
+          <t>office@weinhandel-kohlbacher.at</t>
+        </is>
+      </c>
+      <c r="O850" s="2" t="inlineStr">
+        <is>
+          <t>+43 316 319431</t>
+        </is>
+      </c>
+      <c r="P850" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q850" s="2" t="inlineStr"/>
+      <c r="R850" s="2" t="inlineStr"/>
+      <c r="S850" s="2" t="inlineStr"/>
+      <c r="T850" s="2" t="inlineStr"/>
+      <c r="U850" s="2" t="inlineStr"/>
+      <c r="V850" s="2" t="inlineStr"/>
+      <c r="W850" s="2" t="inlineStr">
+        <is>
+          <t>Anton Kohlbacher</t>
+        </is>
+      </c>
+      <c r="X850" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y850" s="2" t="inlineStr"/>
+      <c r="Z850" s="2" t="inlineStr"/>
+      <c r="AA850" s="2" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Weinkult E.u.</t>
+        </is>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Weinkult E.u.</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>20409</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>Guntramsdorf</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Mödling</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>16 Josef-Lanner-Straße</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>2353</t>
+        </is>
+      </c>
+      <c r="I851" s="2" t="inlineStr">
+        <is>
+          <t>https://weinkult.at</t>
+        </is>
+      </c>
+      <c r="J851" s="2" t="inlineStr"/>
+      <c r="K851" s="2" t="inlineStr"/>
+      <c r="L851" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M851" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N851" s="2" t="inlineStr">
+        <is>
+          <t>office@weinkult.at</t>
+        </is>
+      </c>
+      <c r="O851" s="2" t="inlineStr"/>
+      <c r="P851" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q851" s="2" t="inlineStr">
+        <is>
+          <t>FN264999f</t>
+        </is>
+      </c>
+      <c r="R851" s="2" t="inlineStr"/>
+      <c r="S851" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinothek-WeinKult-459948980864240/</t>
+        </is>
+      </c>
+      <c r="T851" s="2" t="inlineStr"/>
+      <c r="U851" s="2" t="inlineStr"/>
+      <c r="V851" s="2" t="inlineStr"/>
+      <c r="W851" s="2" t="inlineStr">
+        <is>
+          <t>Gerhard Antreich</t>
+        </is>
+      </c>
+      <c r="X851" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y851" s="2" t="inlineStr"/>
+      <c r="Z851" s="2" t="inlineStr"/>
+      <c r="AA851" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gerhard-antreich-8812aa114/</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="inlineStr">
+        <is>
+          <t>Speckbacher Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>Speckbacher Handels Gmbh</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>30873</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>Reutte</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>Tyrol</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>15 Großfeldstraße</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="I852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.speckbacher.at</t>
+        </is>
+      </c>
+      <c r="J852" s="2" t="inlineStr"/>
+      <c r="K852" s="2" t="inlineStr"/>
+      <c r="L852" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M852" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N852" s="2" t="inlineStr">
+        <is>
+          <t>kundenservice@speckbacher.at</t>
+        </is>
+      </c>
+      <c r="O852" s="2" t="inlineStr">
+        <is>
+          <t>+43 5672 62217</t>
+        </is>
+      </c>
+      <c r="P852" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="Q852" s="2" t="inlineStr">
+        <is>
+          <t>FN415717z</t>
+        </is>
+      </c>
+      <c r="R852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eurogast-speckbacher/</t>
+        </is>
+      </c>
+      <c r="S852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/speckbacher.at/</t>
+        </is>
+      </c>
+      <c r="T852" s="2" t="inlineStr"/>
+      <c r="U852" s="2" t="inlineStr"/>
+      <c r="V852" s="2" t="inlineStr"/>
+      <c r="W852" s="2" t="inlineStr">
+        <is>
+          <t>Peter Speckbacher</t>
+        </is>
+      </c>
+      <c r="X852" s="2" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="Y852" s="2" t="inlineStr"/>
+      <c r="Z852" s="2" t="inlineStr"/>
+      <c r="AA852" s="2" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="inlineStr">
+        <is>
+          <t>Vini Mascoli Kg</t>
+        </is>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>Vini Mascoli Kg</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>25324</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>Klaus</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>Vorarlberg</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>17 Treietstraße</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+      <c r="I853" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amicidelvino.at</t>
+        </is>
+      </c>
+      <c r="J853" s="2" t="inlineStr"/>
+      <c r="K853" s="2" t="inlineStr"/>
+      <c r="L853" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M853" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N853" s="2" t="inlineStr">
+        <is>
+          <t>shop@amicidelvino.at</t>
+        </is>
+      </c>
+      <c r="O853" s="2" t="inlineStr"/>
+      <c r="P853" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q853" s="2" t="inlineStr">
+        <is>
+          <t>FN281204k</t>
+        </is>
+      </c>
+      <c r="R853" s="2" t="inlineStr"/>
+      <c r="S853" s="2" t="inlineStr"/>
+      <c r="T853" s="2" t="inlineStr"/>
+      <c r="U853" s="2" t="inlineStr"/>
+      <c r="V853" s="2" t="inlineStr"/>
+      <c r="W853" s="2" t="inlineStr">
+        <is>
+          <t>Markus Ender</t>
+        </is>
+      </c>
+      <c r="X853" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y853" s="2" t="inlineStr"/>
+      <c r="Z853" s="2" t="inlineStr"/>
+      <c r="AA853" s="2" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="inlineStr">
+        <is>
+          <t>Markus Saletz</t>
+        </is>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>Markus Saletz</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>54968</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>Gemeinde Reutte</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Reutte</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr">
+        <is>
+          <t>24 Untermarkt</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="I854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.markus-saletz.at</t>
+        </is>
+      </c>
+      <c r="J854" s="2" t="inlineStr"/>
+      <c r="K854" s="2" t="inlineStr"/>
+      <c r="L854" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M854" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N854" s="2" t="inlineStr">
+        <is>
+          <t>welcome@markus-saletz.at</t>
+        </is>
+      </c>
+      <c r="O854" s="2" t="inlineStr"/>
+      <c r="P854" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q854" s="2" t="inlineStr">
+        <is>
+          <t>ATU68531724</t>
+        </is>
+      </c>
+      <c r="R854" s="2" t="inlineStr"/>
+      <c r="S854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Markus-Saletz-Lieblingsweine-1588202668063142/</t>
+        </is>
+      </c>
+      <c r="T854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/markus_saletz_lieblingsweine/</t>
+        </is>
+      </c>
+      <c r="U854" s="2" t="inlineStr"/>
+      <c r="V854" s="2" t="inlineStr"/>
+      <c r="W854" s="2" t="inlineStr">
+        <is>
+          <t>Markus Saletz</t>
+        </is>
+      </c>
+      <c r="X854" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y854" s="2" t="inlineStr"/>
+      <c r="Z854" s="2" t="inlineStr"/>
+      <c r="AA854" s="2" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="inlineStr">
+        <is>
+          <t>A.b. Bittermann Restaurations Gmbh</t>
+        </is>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>A.b. Bittermann Restaurations Gmbh</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>20419</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>Göttlesbrunn</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Bruck an der Leitha</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>1 Abt-Bruno-Heinrich-Platz</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>2464</t>
+        </is>
+      </c>
+      <c r="I855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adi-bittermann.at</t>
+        </is>
+      </c>
+      <c r="J855" s="2" t="inlineStr"/>
+      <c r="K855" s="2" t="inlineStr"/>
+      <c r="L855" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M855" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N855" s="2" t="inlineStr">
+        <is>
+          <t>info@adi-bittermann.at</t>
+        </is>
+      </c>
+      <c r="O855" s="2" t="inlineStr">
+        <is>
+          <t>+43 2162 81155</t>
+        </is>
+      </c>
+      <c r="P855" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q855" s="2" t="inlineStr">
+        <is>
+          <t>FN246954v</t>
+        </is>
+      </c>
+      <c r="R855" s="2" t="inlineStr"/>
+      <c r="S855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bittermann-vinarium-göttlesbrunn-179273462110267/</t>
+        </is>
+      </c>
+      <c r="T855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bittermannadi/</t>
+        </is>
+      </c>
+      <c r="U855" s="2" t="inlineStr"/>
+      <c r="V855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@adibittermann5167/</t>
+        </is>
+      </c>
+      <c r="W855" s="2" t="inlineStr">
+        <is>
+          <t>Adi Bittermann</t>
+        </is>
+      </c>
+      <c r="X855" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y855" s="2" t="inlineStr"/>
+      <c r="Z855" s="2" t="inlineStr"/>
+      <c r="AA855" s="2" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="inlineStr">
+        <is>
+          <t>Hieber Consulting Gmbh</t>
+        </is>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>Hieber Consulting Gmbh</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>1 Schaukalgasse</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>1170</t>
+        </is>
+      </c>
+      <c r="I856" s="2" t="inlineStr">
+        <is>
+          <t>https://hieber.at</t>
+        </is>
+      </c>
+      <c r="J856" s="2" t="inlineStr"/>
+      <c r="K856" s="2" t="inlineStr"/>
+      <c r="L856" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M856" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N856" s="2" t="inlineStr">
+        <is>
+          <t>trade@hieber.at</t>
+        </is>
+      </c>
+      <c r="O856" s="2" t="inlineStr"/>
+      <c r="P856" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q856" s="2" t="inlineStr">
+        <is>
+          <t>FN265189i</t>
+        </is>
+      </c>
+      <c r="R856" s="2" t="inlineStr"/>
+      <c r="S856" s="2" t="inlineStr"/>
+      <c r="T856" s="2" t="inlineStr"/>
+      <c r="U856" s="2" t="inlineStr"/>
+      <c r="V856" s="2" t="inlineStr"/>
+      <c r="W856" s="2" t="inlineStr">
+        <is>
+          <t>Stefan Hieber</t>
+        </is>
+      </c>
+      <c r="X856" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y856" s="2" t="inlineStr"/>
+      <c r="Z856" s="2" t="inlineStr"/>
+      <c r="AA856" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefan-hieber-0b93a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="inlineStr">
+        <is>
+          <t>Christian Grasl</t>
+        </is>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>Christian Grasl</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>Wilhelmsburg</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>28 Anzengruberstraße</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="I857" s="2" t="inlineStr">
+        <is>
+          <t>http://weinkeller-online.at</t>
+        </is>
+      </c>
+      <c r="J857" s="2" t="inlineStr"/>
+      <c r="K857" s="2" t="inlineStr"/>
+      <c r="L857" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M857" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N857" s="2" t="inlineStr">
+        <is>
+          <t>office@weinkeller-online.at</t>
+        </is>
+      </c>
+      <c r="O857" s="2" t="inlineStr">
+        <is>
+          <t>+43 2746 2807</t>
+        </is>
+      </c>
+      <c r="P857" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q857" s="2" t="inlineStr">
+        <is>
+          <t>ATU54210802</t>
+        </is>
+      </c>
+      <c r="R857" s="2" t="inlineStr"/>
+      <c r="S857" s="2" t="inlineStr"/>
+      <c r="T857" s="2" t="inlineStr"/>
+      <c r="U857" s="2" t="inlineStr"/>
+      <c r="V857" s="2" t="inlineStr"/>
+      <c r="W857" s="2" t="inlineStr">
+        <is>
+          <t>Christian Grasl</t>
+        </is>
+      </c>
+      <c r="X857" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y857" s="2" t="inlineStr"/>
+      <c r="Z857" s="2" t="inlineStr"/>
+      <c r="AA857" s="2" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>53045</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Innsbruck-Land</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>20 Auweg</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="I858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="J858" s="2" t="inlineStr"/>
+      <c r="K858" s="2" t="inlineStr"/>
+      <c r="L858" s="2" t="inlineStr"/>
+      <c r="M858" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N858" s="2" t="inlineStr">
+        <is>
+          <t>marco@beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="O858" s="2" t="inlineStr">
+        <is>
+          <t>+43 5224 22023203</t>
+        </is>
+      </c>
+      <c r="P858" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q858" s="2" t="inlineStr"/>
+      <c r="R858" s="2" t="inlineStr"/>
+      <c r="S858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/beveragecompany.at/</t>
+        </is>
+      </c>
+      <c r="T858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beveragecompany/</t>
+        </is>
+      </c>
+      <c r="U858" s="2" t="inlineStr"/>
+      <c r="V858" s="2" t="inlineStr"/>
+      <c r="W858" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Weingerl</t>
+        </is>
+      </c>
+      <c r="X858" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y858" s="2" t="inlineStr"/>
+      <c r="Z858" s="2" t="inlineStr"/>
+      <c r="AA858" s="2" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Company Ohg</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>53045</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>Wattens</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Innsbruck-Land</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>20 Auweg</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="I859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="J859" s="2" t="inlineStr"/>
+      <c r="K859" s="2" t="inlineStr"/>
+      <c r="L859" s="2" t="inlineStr"/>
+      <c r="M859" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N859" s="2" t="inlineStr">
+        <is>
+          <t>marco@beveragecompany.at</t>
+        </is>
+      </c>
+      <c r="O859" s="2" t="inlineStr">
+        <is>
+          <t>+43 5224 22023203</t>
+        </is>
+      </c>
+      <c r="P859" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q859" s="2" t="inlineStr"/>
+      <c r="R859" s="2" t="inlineStr"/>
+      <c r="S859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/beveragecompany.at/</t>
+        </is>
+      </c>
+      <c r="T859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beveragecompany/</t>
+        </is>
+      </c>
+      <c r="U859" s="2" t="inlineStr"/>
+      <c r="V859" s="2" t="inlineStr"/>
+      <c r="W859" s="2" t="inlineStr">
+        <is>
+          <t>Marco Bachler</t>
+        </is>
+      </c>
+      <c r="X859" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y859" s="2" t="inlineStr"/>
+      <c r="Z859" s="2" t="inlineStr"/>
+      <c r="AA859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marco-bachler-688a2067/</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>Neun Weine Gmbh</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>Neun Weine Gmbh</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>61544</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>Neutal</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland, Oberpullendorf</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>7 Werner von Siemens-Straße</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="I860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.neunweine.at, https://www.neunweine.de</t>
+        </is>
+      </c>
+      <c r="J860" s="2" t="inlineStr"/>
+      <c r="K860" s="2" t="inlineStr"/>
+      <c r="L860" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M860" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N860" s="2" t="inlineStr">
+        <is>
+          <t>michael@neunweine.at</t>
+        </is>
+      </c>
+      <c r="O860" s="2" t="inlineStr">
+        <is>
+          <t>+43 720 3030505099</t>
+        </is>
+      </c>
+      <c r="P860" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q860" s="2" t="inlineStr">
+        <is>
+          <t>FN432466f</t>
+        </is>
+      </c>
+      <c r="R860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neun-weine/</t>
+        </is>
+      </c>
+      <c r="S860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/neunweine/</t>
+        </is>
+      </c>
+      <c r="T860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neunweine/</t>
+        </is>
+      </c>
+      <c r="U860" s="2" t="inlineStr"/>
+      <c r="V860" s="2" t="inlineStr"/>
+      <c r="W860" s="2" t="inlineStr">
+        <is>
+          <t>Michael Pruenner</t>
+        </is>
+      </c>
+      <c r="X860" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder/ Ceo</t>
+        </is>
+      </c>
+      <c r="Y860" s="2" t="inlineStr"/>
+      <c r="Z860" s="2" t="inlineStr"/>
+      <c r="AA860" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/michael-pruenner/</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I861" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J861" s="2" t="inlineStr"/>
+      <c r="K861" s="2" t="inlineStr"/>
+      <c r="L861" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M861" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N861" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O861" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P861" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q861" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R861" s="2" t="inlineStr"/>
+      <c r="S861" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T861" s="2" t="inlineStr"/>
+      <c r="U861" s="2" t="inlineStr"/>
+      <c r="V861" s="2" t="inlineStr"/>
+      <c r="W861" s="2" t="inlineStr">
+        <is>
+          <t>Gerhard Kracher</t>
+        </is>
+      </c>
+      <c r="X861" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Managing Director</t>
+        </is>
+      </c>
+      <c r="Y861" s="2" t="inlineStr"/>
+      <c r="Z861" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA861" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gerhard-kracher-5568b1149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I862" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J862" s="2" t="inlineStr"/>
+      <c r="K862" s="2" t="inlineStr"/>
+      <c r="L862" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M862" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N862" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O862" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P862" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q862" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R862" s="2" t="inlineStr"/>
+      <c r="S862" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T862" s="2" t="inlineStr"/>
+      <c r="U862" s="2" t="inlineStr"/>
+      <c r="V862" s="2" t="inlineStr"/>
+      <c r="W862" s="2" t="inlineStr">
+        <is>
+          <t>Hans Martin</t>
+        </is>
+      </c>
+      <c r="X862" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Manager/ Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y862" s="2" t="inlineStr"/>
+      <c r="Z862" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA862" s="2" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I863" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J863" s="2" t="inlineStr"/>
+      <c r="K863" s="2" t="inlineStr"/>
+      <c r="L863" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M863" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N863" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O863" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P863" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q863" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R863" s="2" t="inlineStr"/>
+      <c r="S863" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T863" s="2" t="inlineStr"/>
+      <c r="U863" s="2" t="inlineStr"/>
+      <c r="V863" s="2" t="inlineStr"/>
+      <c r="W863" s="2" t="inlineStr">
+        <is>
+          <t>Yvonne Kracher</t>
+        </is>
+      </c>
+      <c r="X863" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing And Sales</t>
+        </is>
+      </c>
+      <c r="Y863" s="2" t="inlineStr"/>
+      <c r="Z863" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA863" s="2" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>Kracher Fine Wine Gmbh</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>Illmitz</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>37 Apetlonerstraße</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>7142</t>
+        </is>
+      </c>
+      <c r="I864" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.kracher.at, https://www.finewineshop.com, https://www.kracher.at</t>
+        </is>
+      </c>
+      <c r="J864" s="2" t="inlineStr"/>
+      <c r="K864" s="2" t="inlineStr"/>
+      <c r="L864" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M864" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N864" s="2" t="inlineStr">
+        <is>
+          <t>office@kracher.at</t>
+        </is>
+      </c>
+      <c r="O864" s="2" t="inlineStr">
+        <is>
+          <t>+43 2175 3377</t>
+        </is>
+      </c>
+      <c r="P864" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q864" s="2" t="inlineStr">
+        <is>
+          <t>FN206774f</t>
+        </is>
+      </c>
+      <c r="R864" s="2" t="inlineStr"/>
+      <c r="S864" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kracherfinewine</t>
+        </is>
+      </c>
+      <c r="T864" s="2" t="inlineStr"/>
+      <c r="U864" s="2" t="inlineStr"/>
+      <c r="V864" s="2" t="inlineStr"/>
+      <c r="W864" s="2" t="inlineStr">
+        <is>
+          <t>Hannes Wolf</t>
+        </is>
+      </c>
+      <c r="X864" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y864" s="2" t="inlineStr"/>
+      <c r="Z864" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA864" s="2" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek Eisenberg</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>54996</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch Schützen-Eisenberg</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>1 Am Naturpark</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="I865" s="2" t="inlineStr">
+        <is>
+          <t>https://vinothek.eisenberg.at</t>
+        </is>
+      </c>
+      <c r="J865" s="2" t="inlineStr"/>
+      <c r="K865" s="2" t="inlineStr"/>
+      <c r="L865" s="2" t="inlineStr"/>
+      <c r="M865" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N865" s="2" t="inlineStr">
+        <is>
+          <t>wein@eisenberg.at</t>
+        </is>
+      </c>
+      <c r="O865" s="2" t="inlineStr">
+        <is>
+          <t>+43 3365 2666</t>
+        </is>
+      </c>
+      <c r="P865" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q865" s="2" t="inlineStr"/>
+      <c r="R865" s="2" t="inlineStr"/>
+      <c r="S865" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinothekeisenberg/</t>
+        </is>
+      </c>
+      <c r="T865" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinothek_eisenberg/</t>
+        </is>
+      </c>
+      <c r="U865" s="2" t="inlineStr"/>
+      <c r="V865" s="2" t="inlineStr"/>
+      <c r="W865" s="2" t="inlineStr"/>
+      <c r="X865" s="2" t="inlineStr"/>
+      <c r="Y865" s="2" t="inlineStr"/>
+      <c r="Z865" s="2" t="inlineStr"/>
+      <c r="AA865" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA865"/>
+  <dimension ref="A1:AA866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -85892,6 +85892,99 @@
       <c r="Z865" s="2" t="inlineStr"/>
       <c r="AA865" s="2" t="inlineStr"/>
     </row>
+    <row r="866">
+      <c r="A866" s="2" t="inlineStr">
+        <is>
+          <t>Wein.depot Noitz</t>
+        </is>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>Wein.depot Noitz</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>Furth bei Göttweig</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>169 Römerstraße</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="I866" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wein-handlung.at</t>
+        </is>
+      </c>
+      <c r="J866" s="2" t="inlineStr"/>
+      <c r="K866" s="2" t="inlineStr"/>
+      <c r="L866" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M866" s="2" t="inlineStr"/>
+      <c r="N866" s="2" t="inlineStr">
+        <is>
+          <t>wein.depot@aon.at</t>
+        </is>
+      </c>
+      <c r="O866" s="2" t="inlineStr">
+        <is>
+          <t>+43 2732 85656</t>
+        </is>
+      </c>
+      <c r="P866" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q866" s="2" t="inlineStr">
+        <is>
+          <t>ATU61892946</t>
+        </is>
+      </c>
+      <c r="R866" s="2" t="inlineStr"/>
+      <c r="S866" s="2" t="inlineStr"/>
+      <c r="T866" s="2" t="inlineStr"/>
+      <c r="U866" s="2" t="inlineStr"/>
+      <c r="V866" s="2" t="inlineStr"/>
+      <c r="W866" s="2" t="inlineStr">
+        <is>
+          <t>Franz Noitz</t>
+        </is>
+      </c>
+      <c r="X866" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y866" s="2" t="inlineStr"/>
+      <c r="Z866" s="2" t="inlineStr"/>
+      <c r="AA866" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA866"/>
+  <dimension ref="A1:AA868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -85985,6 +85985,192 @@
       <c r="Z866" s="2" t="inlineStr"/>
       <c r="AA866" s="2" t="inlineStr"/>
     </row>
+    <row r="867">
+      <c r="A867" s="2" t="inlineStr">
+        <is>
+          <t>Maniola Wines e.U.</t>
+        </is>
+      </c>
+      <c r="B867" s="2" t="inlineStr"/>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>167811</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>Perchtoldsdorf</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>Brunnerfeldstraße 71/2</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="I867" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.maniola-wines.com</t>
+        </is>
+      </c>
+      <c r="J867" s="2" t="inlineStr"/>
+      <c r="K867" s="2" t="inlineStr"/>
+      <c r="L867" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M867" s="2" t="inlineStr">
+        <is>
+          <t>102387</t>
+        </is>
+      </c>
+      <c r="N867" s="2" t="inlineStr">
+        <is>
+          <t>office@maniola-wines.com</t>
+        </is>
+      </c>
+      <c r="O867" s="2" t="inlineStr"/>
+      <c r="P867" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q867" s="2" t="inlineStr">
+        <is>
+          <t>FN598530t</t>
+        </is>
+      </c>
+      <c r="R867" s="2" t="inlineStr"/>
+      <c r="S867" s="2" t="inlineStr"/>
+      <c r="T867" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mr_lindemayr/</t>
+        </is>
+      </c>
+      <c r="U867" s="2" t="inlineStr"/>
+      <c r="V867" s="2" t="inlineStr"/>
+      <c r="W867" s="2" t="inlineStr">
+        <is>
+          <t>Manuel Lindemayr</t>
+        </is>
+      </c>
+      <c r="X867" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y867" s="2" t="inlineStr"/>
+      <c r="Z867" s="2" t="inlineStr"/>
+      <c r="AA867" s="2" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="inlineStr">
+        <is>
+          <t>Wein.depot Noitz</t>
+        </is>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>Wein.depot Noitz</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>Furth bei Göttweig</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>Lower Austria</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>169 Römerstraße</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="I868" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wein-handlung.at</t>
+        </is>
+      </c>
+      <c r="J868" s="2" t="inlineStr"/>
+      <c r="K868" s="2" t="inlineStr"/>
+      <c r="L868" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M868" s="2" t="inlineStr"/>
+      <c r="N868" s="2" t="inlineStr">
+        <is>
+          <t>wein.depot@aon.at</t>
+        </is>
+      </c>
+      <c r="O868" s="2" t="inlineStr">
+        <is>
+          <t>+43 2732 85656</t>
+        </is>
+      </c>
+      <c r="P868" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q868" s="2" t="inlineStr">
+        <is>
+          <t>ATU61892946</t>
+        </is>
+      </c>
+      <c r="R868" s="2" t="inlineStr"/>
+      <c r="S868" s="2" t="inlineStr"/>
+      <c r="T868" s="2" t="inlineStr"/>
+      <c r="U868" s="2" t="inlineStr"/>
+      <c r="V868" s="2" t="inlineStr"/>
+      <c r="W868" s="2" t="inlineStr">
+        <is>
+          <t>Franz Noitz</t>
+        </is>
+      </c>
+      <c r="X868" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y868" s="2" t="inlineStr"/>
+      <c r="Z868" s="2" t="inlineStr"/>
+      <c r="AA868" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA868"/>
+  <dimension ref="A1:AA872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -86171,6 +86171,402 @@
       <c r="Z868" s="2" t="inlineStr"/>
       <c r="AA868" s="2" t="inlineStr"/>
     </row>
+    <row r="869">
+      <c r="A869" s="2" t="inlineStr">
+        <is>
+          <t>Lenz Laurenz Maria Moser</t>
+        </is>
+      </c>
+      <c r="B869" s="2" t="inlineStr"/>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>167839</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>Frauenkirchen</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>Burgenland</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>Thermensiedlung 11</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>7132</t>
+        </is>
+      </c>
+      <c r="I869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lenzmoser.at</t>
+        </is>
+      </c>
+      <c r="J869" s="2" t="inlineStr"/>
+      <c r="K869" s="2" t="inlineStr"/>
+      <c r="L869" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M869" s="2" t="inlineStr">
+        <is>
+          <t>739168</t>
+        </is>
+      </c>
+      <c r="N869" s="2" t="inlineStr">
+        <is>
+          <t>office@lenzmoser.at</t>
+        </is>
+      </c>
+      <c r="O869" s="2" t="inlineStr">
+        <is>
+          <t>+43 2732 85541</t>
+        </is>
+      </c>
+      <c r="P869" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q869" s="2" t="inlineStr"/>
+      <c r="R869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/weinkellerei-lenz-moser/</t>
+        </is>
+      </c>
+      <c r="S869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/weinkellereilenzmoser</t>
+        </is>
+      </c>
+      <c r="T869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weinkellerei_lenzmoser/</t>
+        </is>
+      </c>
+      <c r="U869" s="2" t="inlineStr"/>
+      <c r="V869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/LenzMoser1849</t>
+        </is>
+      </c>
+      <c r="W869" s="2" t="inlineStr">
+        <is>
+          <t>Doris Wanek</t>
+        </is>
+      </c>
+      <c r="X869" s="2" t="inlineStr">
+        <is>
+          <t>Export / Sales</t>
+        </is>
+      </c>
+      <c r="Y869" s="2" t="inlineStr"/>
+      <c r="Z869" s="2" t="inlineStr"/>
+      <c r="AA869" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/doris-wanek-178ab0300</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="inlineStr">
+        <is>
+          <t>Rum-exchange Trading Company E.u.</t>
+        </is>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>Rum-exchange Trading Company E.u.</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>145587</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>Dornbirn</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>Vorarlberg</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>3f Bündtlittenstraße</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>6850</t>
+        </is>
+      </c>
+      <c r="I870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rum-exchange.com</t>
+        </is>
+      </c>
+      <c r="J870" s="2" t="inlineStr"/>
+      <c r="K870" s="2" t="inlineStr"/>
+      <c r="L870" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M870" s="2" t="inlineStr"/>
+      <c r="N870" s="2" t="inlineStr">
+        <is>
+          <t>info@rum-exchange.com</t>
+        </is>
+      </c>
+      <c r="O870" s="2" t="inlineStr"/>
+      <c r="P870" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q870" s="2" t="inlineStr">
+        <is>
+          <t>FN509804m</t>
+        </is>
+      </c>
+      <c r="R870" s="2" t="inlineStr"/>
+      <c r="S870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/rumexchangeimport/</t>
+        </is>
+      </c>
+      <c r="T870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rumexchange</t>
+        </is>
+      </c>
+      <c r="U870" s="2" t="inlineStr"/>
+      <c r="V870" s="2" t="inlineStr"/>
+      <c r="W870" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Isopp</t>
+        </is>
+      </c>
+      <c r="X870" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Owner</t>
+        </is>
+      </c>
+      <c r="Y870" s="2" t="inlineStr"/>
+      <c r="Z870" s="2" t="inlineStr"/>
+      <c r="AA870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreas-isopp-8972b6aa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="inlineStr">
+        <is>
+          <t>Unchained Selections</t>
+        </is>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>Unchained Selections</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>88669</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>Ybbs an der Donau</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Melk</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>3 Herrengasse</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="I871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unchainedselections.at</t>
+        </is>
+      </c>
+      <c r="J871" s="2" t="inlineStr"/>
+      <c r="K871" s="2" t="inlineStr"/>
+      <c r="L871" s="2" t="inlineStr"/>
+      <c r="M871" s="2" t="inlineStr"/>
+      <c r="N871" s="2" t="inlineStr">
+        <is>
+          <t>office@unchainedselections.at</t>
+        </is>
+      </c>
+      <c r="O871" s="2" t="inlineStr"/>
+      <c r="P871" s="2" t="inlineStr"/>
+      <c r="Q871" s="2" t="inlineStr"/>
+      <c r="R871" s="2" t="inlineStr"/>
+      <c r="S871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Unchained.Selections/</t>
+        </is>
+      </c>
+      <c r="T871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unchained_selections</t>
+        </is>
+      </c>
+      <c r="U871" s="2" t="inlineStr"/>
+      <c r="V871" s="2" t="inlineStr"/>
+      <c r="W871" s="2" t="inlineStr">
+        <is>
+          <t>Florian Ehn</t>
+        </is>
+      </c>
+      <c r="X871" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Owner</t>
+        </is>
+      </c>
+      <c r="Y871" s="2" t="inlineStr"/>
+      <c r="Z871" s="2" t="inlineStr"/>
+      <c r="AA871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/florian-ehn-8ba17244/</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek VINO</t>
+        </is>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>Vinothek VINO</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>Schärding</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>Upper Austria</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>26 Unterer Stadtplatz</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>4780</t>
+        </is>
+      </c>
+      <c r="I872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vino-schaerding.at</t>
+        </is>
+      </c>
+      <c r="J872" s="2" t="inlineStr"/>
+      <c r="K872" s="2" t="inlineStr"/>
+      <c r="L872" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M872" s="2" t="inlineStr"/>
+      <c r="N872" s="2" t="inlineStr">
+        <is>
+          <t>office@vino-schaerding.at</t>
+        </is>
+      </c>
+      <c r="O872" s="2" t="inlineStr"/>
+      <c r="P872" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q872" s="2" t="inlineStr">
+        <is>
+          <t>ATU64006989</t>
+        </is>
+      </c>
+      <c r="R872" s="2" t="inlineStr"/>
+      <c r="S872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vino.schaerding</t>
+        </is>
+      </c>
+      <c r="T872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinothek_vino_schaerding/</t>
+        </is>
+      </c>
+      <c r="U872" s="2" t="inlineStr"/>
+      <c r="V872" s="2" t="inlineStr"/>
+      <c r="W872" s="2" t="inlineStr">
+        <is>
+          <t>Jens Würz</t>
+        </is>
+      </c>
+      <c r="X872" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y872" s="2" t="inlineStr"/>
+      <c r="Z872" s="2" t="inlineStr"/>
+      <c r="AA872" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA872"/>
+  <dimension ref="A1:AA873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -86567,6 +86567,75 @@
       <c r="Z872" s="2" t="inlineStr"/>
       <c r="AA872" s="2" t="inlineStr"/>
     </row>
+    <row r="873">
+      <c r="A873" s="2" t="inlineStr">
+        <is>
+          <t>Café Vinothek Greisslerei Walletschek</t>
+        </is>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>Café Vinothek Greisslerei Walletschek</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>23398</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>Sobieskiplatz 8</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="I873" s="2" t="inlineStr">
+        <is>
+          <t>https://walletschek.at</t>
+        </is>
+      </c>
+      <c r="J873" s="2" t="inlineStr"/>
+      <c r="K873" s="2" t="inlineStr"/>
+      <c r="L873" s="2" t="inlineStr"/>
+      <c r="M873" s="2" t="inlineStr"/>
+      <c r="N873" s="2" t="inlineStr">
+        <is>
+          <t>cafe.walletschek@chello.at</t>
+        </is>
+      </c>
+      <c r="O873" s="2" t="inlineStr"/>
+      <c r="P873" s="2" t="inlineStr"/>
+      <c r="Q873" s="2" t="inlineStr"/>
+      <c r="R873" s="2" t="inlineStr"/>
+      <c r="S873" s="2" t="inlineStr"/>
+      <c r="T873" s="2" t="inlineStr"/>
+      <c r="U873" s="2" t="inlineStr"/>
+      <c r="V873" s="2" t="inlineStr"/>
+      <c r="W873" s="2" t="inlineStr"/>
+      <c r="X873" s="2" t="inlineStr"/>
+      <c r="Y873" s="2" t="inlineStr"/>
+      <c r="Z873" s="2" t="inlineStr"/>
+      <c r="AA873" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA873"/>
+  <dimension ref="A1:AA875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -86636,6 +86636,192 @@
       <c r="Z873" s="2" t="inlineStr"/>
       <c r="AA873" s="2" t="inlineStr"/>
     </row>
+    <row r="874">
+      <c r="A874" s="2" t="inlineStr">
+        <is>
+          <t>Braunegger Kg</t>
+        </is>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>Braunegger Kg</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>88858</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>Kaltenbach</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>Tirol, Schwaz</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>36 Kaltenbacher Landstraße</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>6272</t>
+        </is>
+      </c>
+      <c r="I874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.braunegger.tirol</t>
+        </is>
+      </c>
+      <c r="J874" s="2" t="inlineStr"/>
+      <c r="K874" s="2" t="inlineStr"/>
+      <c r="L874" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M874" s="2" t="inlineStr"/>
+      <c r="N874" s="2" t="inlineStr">
+        <is>
+          <t>service@braunegger.tirol</t>
+        </is>
+      </c>
+      <c r="O874" s="2" t="inlineStr">
+        <is>
+          <t>+43 5283 2231</t>
+        </is>
+      </c>
+      <c r="P874" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="Q874" s="2" t="inlineStr">
+        <is>
+          <t>FN17468p</t>
+        </is>
+      </c>
+      <c r="R874" s="2" t="inlineStr"/>
+      <c r="S874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/brauneggerkg</t>
+        </is>
+      </c>
+      <c r="T874" s="2" t="inlineStr"/>
+      <c r="U874" s="2" t="inlineStr"/>
+      <c r="V874" s="2" t="inlineStr"/>
+      <c r="W874" s="2" t="inlineStr"/>
+      <c r="X874" s="2" t="inlineStr"/>
+      <c r="Y874" s="2" t="inlineStr"/>
+      <c r="Z874" s="2" t="inlineStr"/>
+      <c r="AA874" s="2" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="inlineStr">
+        <is>
+          <t>Delicando Gmbh</t>
+        </is>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>Delicando Gmbh</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>25115</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>Weiz</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>Steiermark</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>2 Nöstlstraße</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>8160</t>
+        </is>
+      </c>
+      <c r="I875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bigspirits.com, https://www.delicando.com, https://www.reisenhofer.info</t>
+        </is>
+      </c>
+      <c r="J875" s="2" t="inlineStr"/>
+      <c r="K875" s="2" t="inlineStr"/>
+      <c r="L875" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M875" s="2" t="inlineStr"/>
+      <c r="N875" s="2" t="inlineStr">
+        <is>
+          <t>office@delicando.com</t>
+        </is>
+      </c>
+      <c r="O875" s="2" t="inlineStr">
+        <is>
+          <t>+43 3172 60511</t>
+        </is>
+      </c>
+      <c r="P875" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q875" s="2" t="inlineStr">
+        <is>
+          <t>FN317033a</t>
+        </is>
+      </c>
+      <c r="R875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delicando/</t>
+        </is>
+      </c>
+      <c r="S875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delicando.spirits</t>
+        </is>
+      </c>
+      <c r="T875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delicando.spirits/</t>
+        </is>
+      </c>
+      <c r="U875" s="2" t="inlineStr"/>
+      <c r="V875" s="2" t="inlineStr"/>
+      <c r="W875" s="2" t="inlineStr"/>
+      <c r="X875" s="2" t="inlineStr"/>
+      <c r="Y875" s="2" t="inlineStr"/>
+      <c r="Z875" s="2" t="inlineStr"/>
+      <c r="AA875" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA875"/>
+  <dimension ref="A1:AA877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -86822,6 +86822,180 @@
       <c r="Z875" s="2" t="inlineStr"/>
       <c r="AA875" s="2" t="inlineStr"/>
     </row>
+    <row r="876">
+      <c r="A876" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>20420</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>16 Wilhelm-Dachauer-Straße</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I876" s="2" t="inlineStr">
+        <is>
+          <t>https://rarewine.at</t>
+        </is>
+      </c>
+      <c r="J876" s="2" t="inlineStr"/>
+      <c r="K876" s="2" t="inlineStr"/>
+      <c r="L876" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M876" s="2" t="inlineStr"/>
+      <c r="N876" s="2" t="inlineStr">
+        <is>
+          <t>wein@rarewine.at</t>
+        </is>
+      </c>
+      <c r="O876" s="2" t="inlineStr"/>
+      <c r="P876" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q876" s="2" t="inlineStr">
+        <is>
+          <t>FN489451g</t>
+        </is>
+      </c>
+      <c r="R876" s="2" t="inlineStr"/>
+      <c r="S876" s="2" t="inlineStr"/>
+      <c r="T876" s="2" t="inlineStr"/>
+      <c r="U876" s="2" t="inlineStr"/>
+      <c r="V876" s="2" t="inlineStr"/>
+      <c r="W876" s="2" t="inlineStr">
+        <is>
+          <t>Robert G.</t>
+        </is>
+      </c>
+      <c r="X876" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y876" s="2" t="inlineStr"/>
+      <c r="Z876" s="2" t="inlineStr"/>
+      <c r="AA876" s="2" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>88906</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Peter in der Au-Markt</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Amstetten</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>19 Marktplatz</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="I877" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="J877" s="2" t="inlineStr"/>
+      <c r="K877" s="2" t="inlineStr"/>
+      <c r="L877" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M877" s="2" t="inlineStr"/>
+      <c r="N877" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="O877" s="2" t="inlineStr">
+        <is>
+          <t>+43 7477 42323</t>
+        </is>
+      </c>
+      <c r="P877" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q877" s="2" t="inlineStr">
+        <is>
+          <t>FN21555z</t>
+        </is>
+      </c>
+      <c r="R877" s="2" t="inlineStr"/>
+      <c r="S877" s="2" t="inlineStr"/>
+      <c r="T877" s="2" t="inlineStr"/>
+      <c r="U877" s="2" t="inlineStr"/>
+      <c r="V877" s="2" t="inlineStr"/>
+      <c r="W877" s="2" t="inlineStr"/>
+      <c r="X877" s="2" t="inlineStr"/>
+      <c r="Y877" s="2" t="inlineStr"/>
+      <c r="Z877" s="2" t="inlineStr"/>
+      <c r="AA877" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA877"/>
+  <dimension ref="A1:AA880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -86996,6 +86996,257 @@
       <c r="Z877" s="2" t="inlineStr"/>
       <c r="AA877" s="2" t="inlineStr"/>
     </row>
+    <row r="878">
+      <c r="A878" s="2" t="inlineStr">
+        <is>
+          <t>Klausner Wein &amp; Service</t>
+        </is>
+      </c>
+      <c r="B878" s="2" t="inlineStr"/>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>168346</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>Wiesing</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr"/>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>Bradl 321</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="I878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klausner.wine</t>
+        </is>
+      </c>
+      <c r="J878" s="2" t="inlineStr"/>
+      <c r="K878" s="2" t="inlineStr"/>
+      <c r="L878" s="2" t="inlineStr"/>
+      <c r="M878" s="2" t="inlineStr"/>
+      <c r="N878" s="2" t="inlineStr">
+        <is>
+          <t>info@klausner.wine</t>
+        </is>
+      </c>
+      <c r="O878" s="2" t="inlineStr"/>
+      <c r="P878" s="2" t="inlineStr"/>
+      <c r="Q878" s="2" t="inlineStr"/>
+      <c r="R878" s="2" t="inlineStr"/>
+      <c r="S878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Klausner-Wein-Service-281094342272921/</t>
+        </is>
+      </c>
+      <c r="T878" s="2" t="inlineStr"/>
+      <c r="U878" s="2" t="inlineStr"/>
+      <c r="V878" s="2" t="inlineStr"/>
+      <c r="W878" s="2" t="inlineStr">
+        <is>
+          <t>Sandro Klausner</t>
+        </is>
+      </c>
+      <c r="X878" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y878" s="2" t="inlineStr"/>
+      <c r="Z878" s="2" t="inlineStr"/>
+      <c r="AA878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sandro-klausner-58a75b92/</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>20420</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>16 Wilhelm-Dachauer-Straße</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I879" s="2" t="inlineStr">
+        <is>
+          <t>https://rarewine.at</t>
+        </is>
+      </c>
+      <c r="J879" s="2" t="inlineStr"/>
+      <c r="K879" s="2" t="inlineStr"/>
+      <c r="L879" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M879" s="2" t="inlineStr"/>
+      <c r="N879" s="2" t="inlineStr">
+        <is>
+          <t>wein@rarewine.at</t>
+        </is>
+      </c>
+      <c r="O879" s="2" t="inlineStr"/>
+      <c r="P879" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q879" s="2" t="inlineStr">
+        <is>
+          <t>FN489451g</t>
+        </is>
+      </c>
+      <c r="R879" s="2" t="inlineStr"/>
+      <c r="S879" s="2" t="inlineStr"/>
+      <c r="T879" s="2" t="inlineStr"/>
+      <c r="U879" s="2" t="inlineStr"/>
+      <c r="V879" s="2" t="inlineStr"/>
+      <c r="W879" s="2" t="inlineStr">
+        <is>
+          <t>Robert G.</t>
+        </is>
+      </c>
+      <c r="X879" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y879" s="2" t="inlineStr"/>
+      <c r="Z879" s="2" t="inlineStr"/>
+      <c r="AA879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>88906</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Peter in der Au-Markt</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Amstetten</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>19 Marktplatz</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="I880" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="J880" s="2" t="inlineStr"/>
+      <c r="K880" s="2" t="inlineStr"/>
+      <c r="L880" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M880" s="2" t="inlineStr"/>
+      <c r="N880" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="O880" s="2" t="inlineStr">
+        <is>
+          <t>+43 7477 42323</t>
+        </is>
+      </c>
+      <c r="P880" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q880" s="2" t="inlineStr">
+        <is>
+          <t>FN21555z</t>
+        </is>
+      </c>
+      <c r="R880" s="2" t="inlineStr"/>
+      <c r="S880" s="2" t="inlineStr"/>
+      <c r="T880" s="2" t="inlineStr"/>
+      <c r="U880" s="2" t="inlineStr"/>
+      <c r="V880" s="2" t="inlineStr"/>
+      <c r="W880" s="2" t="inlineStr"/>
+      <c r="X880" s="2" t="inlineStr"/>
+      <c r="Y880" s="2" t="inlineStr"/>
+      <c r="Z880" s="2" t="inlineStr"/>
+      <c r="AA880" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA880"/>
+  <dimension ref="A1:AA882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -87247,6 +87247,180 @@
       <c r="Z880" s="2" t="inlineStr"/>
       <c r="AA880" s="2" t="inlineStr"/>
     </row>
+    <row r="881">
+      <c r="A881" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>20420</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>16 Wilhelm-Dachauer-Straße</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I881" s="2" t="inlineStr">
+        <is>
+          <t>https://rarewine.at</t>
+        </is>
+      </c>
+      <c r="J881" s="2" t="inlineStr"/>
+      <c r="K881" s="2" t="inlineStr"/>
+      <c r="L881" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M881" s="2" t="inlineStr"/>
+      <c r="N881" s="2" t="inlineStr">
+        <is>
+          <t>wein@rarewine.at</t>
+        </is>
+      </c>
+      <c r="O881" s="2" t="inlineStr"/>
+      <c r="P881" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q881" s="2" t="inlineStr">
+        <is>
+          <t>FN489451g</t>
+        </is>
+      </c>
+      <c r="R881" s="2" t="inlineStr"/>
+      <c r="S881" s="2" t="inlineStr"/>
+      <c r="T881" s="2" t="inlineStr"/>
+      <c r="U881" s="2" t="inlineStr"/>
+      <c r="V881" s="2" t="inlineStr"/>
+      <c r="W881" s="2" t="inlineStr">
+        <is>
+          <t>Robert G.</t>
+        </is>
+      </c>
+      <c r="X881" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y881" s="2" t="inlineStr"/>
+      <c r="Z881" s="2" t="inlineStr"/>
+      <c r="AA881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>88906</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Peter in der Au-Markt</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Amstetten</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>19 Marktplatz</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="I882" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="J882" s="2" t="inlineStr"/>
+      <c r="K882" s="2" t="inlineStr"/>
+      <c r="L882" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M882" s="2" t="inlineStr"/>
+      <c r="N882" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="O882" s="2" t="inlineStr">
+        <is>
+          <t>+43 7477 42323</t>
+        </is>
+      </c>
+      <c r="P882" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q882" s="2" t="inlineStr">
+        <is>
+          <t>FN21555z</t>
+        </is>
+      </c>
+      <c r="R882" s="2" t="inlineStr"/>
+      <c r="S882" s="2" t="inlineStr"/>
+      <c r="T882" s="2" t="inlineStr"/>
+      <c r="U882" s="2" t="inlineStr"/>
+      <c r="V882" s="2" t="inlineStr"/>
+      <c r="W882" s="2" t="inlineStr"/>
+      <c r="X882" s="2" t="inlineStr"/>
+      <c r="Y882" s="2" t="inlineStr"/>
+      <c r="Z882" s="2" t="inlineStr"/>
+      <c r="AA882" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA882"/>
+  <dimension ref="A1:AA884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -87421,6 +87421,180 @@
       <c r="Z882" s="2" t="inlineStr"/>
       <c r="AA882" s="2" t="inlineStr"/>
     </row>
+    <row r="883">
+      <c r="A883" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>20420</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>16 Wilhelm-Dachauer-Straße</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I883" s="2" t="inlineStr">
+        <is>
+          <t>https://rarewine.at</t>
+        </is>
+      </c>
+      <c r="J883" s="2" t="inlineStr"/>
+      <c r="K883" s="2" t="inlineStr"/>
+      <c r="L883" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M883" s="2" t="inlineStr"/>
+      <c r="N883" s="2" t="inlineStr">
+        <is>
+          <t>wein@rarewine.at</t>
+        </is>
+      </c>
+      <c r="O883" s="2" t="inlineStr"/>
+      <c r="P883" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q883" s="2" t="inlineStr">
+        <is>
+          <t>FN489451g</t>
+        </is>
+      </c>
+      <c r="R883" s="2" t="inlineStr"/>
+      <c r="S883" s="2" t="inlineStr"/>
+      <c r="T883" s="2" t="inlineStr"/>
+      <c r="U883" s="2" t="inlineStr"/>
+      <c r="V883" s="2" t="inlineStr"/>
+      <c r="W883" s="2" t="inlineStr">
+        <is>
+          <t>Robert G.</t>
+        </is>
+      </c>
+      <c r="X883" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y883" s="2" t="inlineStr"/>
+      <c r="Z883" s="2" t="inlineStr"/>
+      <c r="AA883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>88906</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Peter in der Au-Markt</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Amstetten</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>19 Marktplatz</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="I884" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="J884" s="2" t="inlineStr"/>
+      <c r="K884" s="2" t="inlineStr"/>
+      <c r="L884" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M884" s="2" t="inlineStr"/>
+      <c r="N884" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="O884" s="2" t="inlineStr">
+        <is>
+          <t>+43 7477 42323</t>
+        </is>
+      </c>
+      <c r="P884" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q884" s="2" t="inlineStr">
+        <is>
+          <t>FN21555z</t>
+        </is>
+      </c>
+      <c r="R884" s="2" t="inlineStr"/>
+      <c r="S884" s="2" t="inlineStr"/>
+      <c r="T884" s="2" t="inlineStr"/>
+      <c r="U884" s="2" t="inlineStr"/>
+      <c r="V884" s="2" t="inlineStr"/>
+      <c r="W884" s="2" t="inlineStr"/>
+      <c r="X884" s="2" t="inlineStr"/>
+      <c r="Y884" s="2" t="inlineStr"/>
+      <c r="Z884" s="2" t="inlineStr"/>
+      <c r="AA884" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Austria.xlsx
+++ b/BWI/bestwine_output/bestwine_Austria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA884"/>
+  <dimension ref="A1:AA886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -87595,6 +87595,180 @@
       <c r="Z884" s="2" t="inlineStr"/>
       <c r="AA884" s="2" t="inlineStr"/>
     </row>
+    <row r="885">
+      <c r="A885" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>Rarewine Austria Gmbh</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>20420</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>16 Wilhelm-Dachauer-Straße</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I885" s="2" t="inlineStr">
+        <is>
+          <t>https://rarewine.at</t>
+        </is>
+      </c>
+      <c r="J885" s="2" t="inlineStr"/>
+      <c r="K885" s="2" t="inlineStr"/>
+      <c r="L885" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M885" s="2" t="inlineStr"/>
+      <c r="N885" s="2" t="inlineStr">
+        <is>
+          <t>wein@rarewine.at</t>
+        </is>
+      </c>
+      <c r="O885" s="2" t="inlineStr"/>
+      <c r="P885" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q885" s="2" t="inlineStr">
+        <is>
+          <t>FN489451g</t>
+        </is>
+      </c>
+      <c r="R885" s="2" t="inlineStr"/>
+      <c r="S885" s="2" t="inlineStr"/>
+      <c r="T885" s="2" t="inlineStr"/>
+      <c r="U885" s="2" t="inlineStr"/>
+      <c r="V885" s="2" t="inlineStr"/>
+      <c r="W885" s="2" t="inlineStr">
+        <is>
+          <t>Robert G.</t>
+        </is>
+      </c>
+      <c r="X885" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y885" s="2" t="inlineStr"/>
+      <c r="Z885" s="2" t="inlineStr"/>
+      <c r="AA885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>Zach Getränkehandel Gmbh &amp; Co. Kg</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>88906</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>Sankt Peter in der Au-Markt</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>Niederösterreich, Amstetten</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>19 Marktplatz</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="I886" s="2" t="inlineStr">
+        <is>
+          <t>https://www.getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="J886" s="2" t="inlineStr"/>
+      <c r="K886" s="2" t="inlineStr"/>
+      <c r="L886" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M886" s="2" t="inlineStr"/>
+      <c r="N886" s="2" t="inlineStr">
+        <is>
+          <t>office@getraenke-zach.at</t>
+        </is>
+      </c>
+      <c r="O886" s="2" t="inlineStr">
+        <is>
+          <t>+43 7477 42323</t>
+        </is>
+      </c>
+      <c r="P886" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q886" s="2" t="inlineStr">
+        <is>
+          <t>FN21555z</t>
+        </is>
+      </c>
+      <c r="R886" s="2" t="inlineStr"/>
+      <c r="S886" s="2" t="inlineStr"/>
+      <c r="T886" s="2" t="inlineStr"/>
+      <c r="U886" s="2" t="inlineStr"/>
+      <c r="V886" s="2" t="inlineStr"/>
+      <c r="W886" s="2" t="inlineStr"/>
+      <c r="X886" s="2" t="inlineStr"/>
+      <c r="Y886" s="2" t="inlineStr"/>
+      <c r="Z886" s="2" t="inlineStr"/>
+      <c r="AA886" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
